--- a/30_table/01_테스트버전/Table_Data_Item.xlsx
+++ b/30_table/01_테스트버전/Table_Data_Item.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1592" uniqueCount="459">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1604" uniqueCount="461">
   <si>
     <t>작업자</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1612,6 +1612,14 @@
   </si>
   <si>
     <t>drop_0027</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>좀비의 영혼</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>item_quest_02</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -5845,7 +5853,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet3"/>
-  <dimension ref="A1:AE120"/>
+  <dimension ref="A1:AE121"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="6.5" style="37" bestFit="1" customWidth="1"/>
@@ -9895,7 +9903,7 @@
         <v>STR_ITEM_EQUIP_R_AC_01_DESC</v>
       </c>
       <c r="F45" s="34">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G45" s="34" t="s">
         <v>46</v>
@@ -9913,7 +9921,7 @@
         <v>0</v>
       </c>
       <c r="L45" s="34">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="M45" s="34">
         <v>0</v>
@@ -9989,7 +9997,7 @@
         <v>STR_ITEM_EQUIP_R_AC_02_DESC</v>
       </c>
       <c r="F46" s="34">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G46" s="34" t="s">
         <v>46</v>
@@ -10007,7 +10015,7 @@
         <v>0</v>
       </c>
       <c r="L46" s="34">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="M46" s="34">
         <v>0</v>
@@ -10083,7 +10091,7 @@
         <v>STR_ITEM_EQUIP_R_AC_03_DESC</v>
       </c>
       <c r="F47" s="34">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G47" s="34" t="s">
         <v>46</v>
@@ -10101,7 +10109,7 @@
         <v>3</v>
       </c>
       <c r="L47" s="34">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="M47" s="34">
         <v>0</v>
@@ -10177,7 +10185,7 @@
         <v>STR_ITEM_EQUIP_R_AC_04_DESC</v>
       </c>
       <c r="F48" s="34">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G48" s="34" t="s">
         <v>46</v>
@@ -10195,7 +10203,7 @@
         <v>0</v>
       </c>
       <c r="L48" s="34">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="M48" s="34">
         <v>3</v>
@@ -10271,7 +10279,7 @@
         <v>STR_ITEM_EQUIP_R_AC_05_DESC</v>
       </c>
       <c r="F49" s="34">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G49" s="34" t="s">
         <v>46</v>
@@ -10289,7 +10297,7 @@
         <v>0</v>
       </c>
       <c r="L49" s="34">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="M49" s="34">
         <v>0</v>
@@ -14758,11 +14766,11 @@
         <v>111</v>
       </c>
       <c r="D100" s="39" t="str">
-        <f t="shared" ref="D100:D114" si="44">"STR_"&amp;UPPER(C100)</f>
+        <f t="shared" ref="D100:D115" si="44">"STR_"&amp;UPPER(C100)</f>
         <v>STR_ITEM_BOX_01</v>
       </c>
       <c r="E100" s="39" t="str">
-        <f t="shared" ref="E100:E114" si="45">D100&amp;"_DESC"</f>
+        <f t="shared" ref="E100:E115" si="45">D100&amp;"_DESC"</f>
         <v>STR_ITEM_BOX_01_DESC</v>
       </c>
       <c r="F100" s="39">
@@ -15414,7 +15422,7 @@
         <v>STR_ITEM_BOX_09_DESC</v>
       </c>
       <c r="F108" s="39">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G108" s="39" t="s">
         <v>50</v>
@@ -15832,202 +15840,202 @@
       </c>
     </row>
     <row r="113" spans="1:31" x14ac:dyDescent="0.3">
-      <c r="A113" s="34">
+      <c r="A113" s="39">
+        <v>38001</v>
+      </c>
+      <c r="B113" s="40" t="s">
+        <v>459</v>
+      </c>
+      <c r="C113" s="41" t="s">
+        <v>460</v>
+      </c>
+      <c r="D113" s="39" t="str">
+        <f t="shared" ref="D113" si="56">"STR_"&amp;UPPER(C113)</f>
+        <v>STR_ITEM_QUEST_02</v>
+      </c>
+      <c r="E113" s="39" t="str">
+        <f t="shared" ref="E113" si="57">D113&amp;"_DESC"</f>
+        <v>STR_ITEM_QUEST_02_DESC</v>
+      </c>
+      <c r="F113" s="39">
+        <v>0</v>
+      </c>
+      <c r="G113" s="39" t="s">
+        <v>54</v>
+      </c>
+      <c r="H113" s="39">
+        <v>0</v>
+      </c>
+      <c r="I113" s="39">
+        <v>0</v>
+      </c>
+      <c r="J113" s="39">
+        <v>0</v>
+      </c>
+      <c r="K113" s="39">
+        <v>0</v>
+      </c>
+      <c r="L113" s="39">
+        <v>0</v>
+      </c>
+      <c r="M113" s="39">
+        <v>0</v>
+      </c>
+      <c r="N113" s="39">
+        <v>0</v>
+      </c>
+      <c r="O113" s="39"/>
+      <c r="P113" s="39" t="s">
+        <v>44</v>
+      </c>
+      <c r="Q113" s="39">
+        <v>0</v>
+      </c>
+      <c r="R113" s="39" t="s">
+        <v>41</v>
+      </c>
+      <c r="S113" s="39"/>
+      <c r="T113" s="39"/>
+      <c r="U113" s="39" t="s">
+        <v>41</v>
+      </c>
+      <c r="V113" s="39" t="s">
+        <v>41</v>
+      </c>
+      <c r="W113" s="39" t="b">
+        <v>1</v>
+      </c>
+      <c r="X113" s="39">
+        <v>10</v>
+      </c>
+      <c r="Y113" s="39">
+        <v>0</v>
+      </c>
+      <c r="Z113" s="39" t="s">
+        <v>41</v>
+      </c>
+      <c r="AA113" s="39">
+        <v>0</v>
+      </c>
+      <c r="AB113" s="39" t="s">
+        <v>125</v>
+      </c>
+      <c r="AC113" s="39" t="s">
+        <v>41</v>
+      </c>
+      <c r="AD113" s="39" t="s">
+        <v>41</v>
+      </c>
+      <c r="AE113" s="39" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="114" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="A114" s="34">
         <v>38500</v>
       </c>
-      <c r="B113" s="35" t="s">
+      <c r="B114" s="35" t="s">
         <v>171</v>
       </c>
-      <c r="C113" s="36" t="s">
+      <c r="C114" s="36" t="s">
         <v>113</v>
       </c>
-      <c r="D113" s="34" t="str">
+      <c r="D114" s="34" t="str">
         <f t="shared" si="44"/>
         <v>STR_ITEM_METERIAL_01</v>
       </c>
-      <c r="E113" s="34" t="str">
+      <c r="E114" s="34" t="str">
         <f t="shared" si="45"/>
         <v>STR_ITEM_METERIAL_01_DESC</v>
       </c>
-      <c r="F113" s="34">
-        <v>0</v>
-      </c>
-      <c r="G113" s="34" t="s">
+      <c r="F114" s="34">
+        <v>0</v>
+      </c>
+      <c r="G114" s="34" t="s">
         <v>56</v>
       </c>
-      <c r="H113" s="34">
-        <v>0</v>
-      </c>
-      <c r="I113" s="34">
-        <v>0</v>
-      </c>
-      <c r="J113" s="34">
-        <v>0</v>
-      </c>
-      <c r="K113" s="34">
-        <v>0</v>
-      </c>
-      <c r="L113" s="34">
-        <v>0</v>
-      </c>
-      <c r="M113" s="34">
-        <v>0</v>
-      </c>
-      <c r="N113" s="34">
-        <v>0</v>
-      </c>
-      <c r="P113" s="34" t="s">
+      <c r="H114" s="34">
+        <v>0</v>
+      </c>
+      <c r="I114" s="34">
+        <v>0</v>
+      </c>
+      <c r="J114" s="34">
+        <v>0</v>
+      </c>
+      <c r="K114" s="34">
+        <v>0</v>
+      </c>
+      <c r="L114" s="34">
+        <v>0</v>
+      </c>
+      <c r="M114" s="34">
+        <v>0</v>
+      </c>
+      <c r="N114" s="34">
+        <v>0</v>
+      </c>
+      <c r="P114" s="34" t="s">
         <v>44</v>
       </c>
-      <c r="Q113" s="34">
-        <v>0</v>
-      </c>
-      <c r="R113" s="37" t="s">
-        <v>41</v>
-      </c>
-      <c r="U113" s="37" t="s">
-        <v>41</v>
-      </c>
-      <c r="V113" s="37" t="s">
-        <v>41</v>
-      </c>
-      <c r="W113" s="34" t="b">
+      <c r="Q114" s="34">
+        <v>0</v>
+      </c>
+      <c r="R114" s="37" t="s">
+        <v>41</v>
+      </c>
+      <c r="U114" s="37" t="s">
+        <v>41</v>
+      </c>
+      <c r="V114" s="37" t="s">
+        <v>41</v>
+      </c>
+      <c r="W114" s="34" t="b">
         <v>1</v>
       </c>
-      <c r="X113" s="34">
+      <c r="X114" s="34">
         <v>10</v>
       </c>
-      <c r="Y113" s="34">
-        <v>0</v>
-      </c>
-      <c r="Z113" s="34" t="s">
-        <v>41</v>
-      </c>
-      <c r="AA113" s="37">
-        <v>0</v>
-      </c>
-      <c r="AB113" s="37" t="s">
+      <c r="Y114" s="34">
+        <v>0</v>
+      </c>
+      <c r="Z114" s="34" t="s">
+        <v>41</v>
+      </c>
+      <c r="AA114" s="37">
+        <v>0</v>
+      </c>
+      <c r="AB114" s="37" t="s">
         <v>125</v>
       </c>
-      <c r="AC113" s="37" t="s">
-        <v>41</v>
-      </c>
-      <c r="AD113" s="37" t="s">
-        <v>41</v>
-      </c>
-      <c r="AE113" s="37" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="114" spans="1:31" x14ac:dyDescent="0.3">
-      <c r="A114" s="39">
+      <c r="AC114" s="37" t="s">
+        <v>41</v>
+      </c>
+      <c r="AD114" s="37" t="s">
+        <v>41</v>
+      </c>
+      <c r="AE114" s="37" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="115" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="A115" s="39">
         <v>39000</v>
       </c>
-      <c r="B114" s="40" t="s">
+      <c r="B115" s="40" t="s">
         <v>172</v>
       </c>
-      <c r="C114" s="41" t="s">
+      <c r="C115" s="41" t="s">
         <v>162</v>
       </c>
-      <c r="D114" s="39" t="str">
+      <c r="D115" s="39" t="str">
         <f t="shared" si="44"/>
         <v>STR_ITEM_POTION_ITEMSLOT_01</v>
       </c>
-      <c r="E114" s="39" t="str">
+      <c r="E115" s="39" t="str">
         <f t="shared" si="45"/>
         <v>STR_ITEM_POTION_ITEMSLOT_01_DESC</v>
       </c>
-      <c r="F114" s="39">
-        <v>0</v>
-      </c>
-      <c r="G114" s="39" t="s">
-        <v>48</v>
-      </c>
-      <c r="H114" s="39">
-        <v>0</v>
-      </c>
-      <c r="I114" s="39">
-        <v>0</v>
-      </c>
-      <c r="J114" s="39">
-        <v>0</v>
-      </c>
-      <c r="K114" s="39">
-        <v>0</v>
-      </c>
-      <c r="L114" s="39">
-        <v>0</v>
-      </c>
-      <c r="M114" s="39">
-        <v>0</v>
-      </c>
-      <c r="N114" s="39">
-        <v>0</v>
-      </c>
-      <c r="O114" s="39"/>
-      <c r="P114" s="39" t="s">
-        <v>163</v>
-      </c>
-      <c r="Q114" s="39">
-        <v>5</v>
-      </c>
-      <c r="R114" s="39" t="s">
-        <v>41</v>
-      </c>
-      <c r="S114" s="39"/>
-      <c r="T114" s="39"/>
-      <c r="U114" s="39" t="s">
-        <v>41</v>
-      </c>
-      <c r="V114" s="39" t="s">
-        <v>41</v>
-      </c>
-      <c r="W114" s="39" t="b">
-        <v>1</v>
-      </c>
-      <c r="X114" s="39">
-        <v>10</v>
-      </c>
-      <c r="Y114" s="39">
-        <v>25</v>
-      </c>
-      <c r="Z114" s="39" t="s">
-        <v>41</v>
-      </c>
-      <c r="AA114" s="39">
-        <v>0</v>
-      </c>
-      <c r="AB114" s="39" t="s">
-        <v>302</v>
-      </c>
-      <c r="AC114" s="39" t="s">
-        <v>41</v>
-      </c>
-      <c r="AD114" s="39" t="s">
-        <v>41</v>
-      </c>
-      <c r="AE114" s="39" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="115" spans="1:31" x14ac:dyDescent="0.3">
-      <c r="A115" s="39">
-        <v>39001</v>
-      </c>
-      <c r="B115" s="40" t="s">
-        <v>173</v>
-      </c>
-      <c r="C115" s="41" t="s">
-        <v>166</v>
-      </c>
-      <c r="D115" s="39" t="str">
-        <f t="shared" ref="D115" si="56">"STR_"&amp;UPPER(C115)</f>
-        <v>STR_ITEM_POTION_SLOT_01</v>
-      </c>
-      <c r="E115" s="39" t="str">
-        <f t="shared" ref="E115" si="57">D115&amp;"_DESC"</f>
-        <v>STR_ITEM_POTION_SLOT_01_DESC</v>
-      </c>
       <c r="F115" s="39">
         <v>0</v>
       </c>
@@ -16057,10 +16065,10 @@
       </c>
       <c r="O115" s="39"/>
       <c r="P115" s="39" t="s">
-        <v>263</v>
+        <v>163</v>
       </c>
       <c r="Q115" s="39">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="R115" s="39" t="s">
         <v>41</v>
@@ -16080,7 +16088,7 @@
         <v>10</v>
       </c>
       <c r="Y115" s="39">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="Z115" s="39" t="s">
         <v>41</v>
@@ -16089,7 +16097,7 @@
         <v>0</v>
       </c>
       <c r="AB115" s="39" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="AC115" s="39" t="s">
         <v>41</v>
@@ -16103,24 +16111,24 @@
     </row>
     <row r="116" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A116" s="39">
-        <v>39002</v>
+        <v>39001</v>
       </c>
       <c r="B116" s="40" t="s">
-        <v>440</v>
+        <v>173</v>
       </c>
       <c r="C116" s="41" t="s">
-        <v>437</v>
+        <v>166</v>
       </c>
       <c r="D116" s="39" t="str">
         <f t="shared" ref="D116" si="58">"STR_"&amp;UPPER(C116)</f>
-        <v>STR_ITEM_SUMMON_01</v>
+        <v>STR_ITEM_POTION_SLOT_01</v>
       </c>
       <c r="E116" s="39" t="str">
         <f t="shared" ref="E116" si="59">D116&amp;"_DESC"</f>
-        <v>STR_ITEM_SUMMON_01_DESC</v>
+        <v>STR_ITEM_POTION_SLOT_01_DESC</v>
       </c>
       <c r="F116" s="39">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G116" s="39" t="s">
         <v>48</v>
@@ -16148,10 +16156,10 @@
       </c>
       <c r="O116" s="39"/>
       <c r="P116" s="39" t="s">
-        <v>438</v>
+        <v>263</v>
       </c>
       <c r="Q116" s="39">
-        <v>10017</v>
+        <v>1</v>
       </c>
       <c r="R116" s="39" t="s">
         <v>41</v>
@@ -16171,7 +16179,7 @@
         <v>10</v>
       </c>
       <c r="Y116" s="39">
-        <v>125</v>
+        <v>50</v>
       </c>
       <c r="Z116" s="39" t="s">
         <v>41</v>
@@ -16180,7 +16188,7 @@
         <v>0</v>
       </c>
       <c r="AB116" s="39" t="s">
-        <v>439</v>
+        <v>303</v>
       </c>
       <c r="AC116" s="39" t="s">
         <v>41</v>
@@ -16194,21 +16202,21 @@
     </row>
     <row r="117" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A117" s="39">
-        <v>39003</v>
+        <v>39002</v>
       </c>
       <c r="B117" s="40" t="s">
-        <v>446</v>
+        <v>440</v>
       </c>
       <c r="C117" s="41" t="s">
-        <v>442</v>
+        <v>437</v>
       </c>
       <c r="D117" s="39" t="str">
-        <f t="shared" ref="D117:D119" si="60">"STR_"&amp;UPPER(C117)</f>
-        <v>STR_ITEM_SUMMON_02</v>
+        <f t="shared" ref="D117" si="60">"STR_"&amp;UPPER(C117)</f>
+        <v>STR_ITEM_SUMMON_01</v>
       </c>
       <c r="E117" s="39" t="str">
-        <f t="shared" ref="E117:E119" si="61">D117&amp;"_DESC"</f>
-        <v>STR_ITEM_SUMMON_02_DESC</v>
+        <f t="shared" ref="E117" si="61">D117&amp;"_DESC"</f>
+        <v>STR_ITEM_SUMMON_01_DESC</v>
       </c>
       <c r="F117" s="39">
         <v>4</v>
@@ -16242,7 +16250,7 @@
         <v>438</v>
       </c>
       <c r="Q117" s="39">
-        <v>10018</v>
+        <v>10017</v>
       </c>
       <c r="R117" s="39" t="s">
         <v>41</v>
@@ -16285,21 +16293,21 @@
     </row>
     <row r="118" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A118" s="39">
-        <v>39004</v>
+        <v>39003</v>
       </c>
       <c r="B118" s="40" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="C118" s="41" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="D118" s="39" t="str">
-        <f t="shared" si="60"/>
-        <v>STR_ITEM_SUMMON_03</v>
+        <f t="shared" ref="D118:D120" si="62">"STR_"&amp;UPPER(C118)</f>
+        <v>STR_ITEM_SUMMON_02</v>
       </c>
       <c r="E118" s="39" t="str">
-        <f t="shared" si="61"/>
-        <v>STR_ITEM_SUMMON_03_DESC</v>
+        <f t="shared" ref="E118:E120" si="63">D118&amp;"_DESC"</f>
+        <v>STR_ITEM_SUMMON_02_DESC</v>
       </c>
       <c r="F118" s="39">
         <v>4</v>
@@ -16333,7 +16341,7 @@
         <v>438</v>
       </c>
       <c r="Q118" s="39">
-        <v>10019</v>
+        <v>10018</v>
       </c>
       <c r="R118" s="39" t="s">
         <v>41</v>
@@ -16376,21 +16384,21 @@
     </row>
     <row r="119" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A119" s="39">
-        <v>39005</v>
+        <v>39004</v>
       </c>
       <c r="B119" s="40" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="C119" s="41" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="D119" s="39" t="str">
-        <f t="shared" si="60"/>
-        <v>STR_ITEM_SUMMON_04</v>
+        <f t="shared" si="62"/>
+        <v>STR_ITEM_SUMMON_03</v>
       </c>
       <c r="E119" s="39" t="str">
-        <f t="shared" si="61"/>
-        <v>STR_ITEM_SUMMON_04_DESC</v>
+        <f t="shared" si="63"/>
+        <v>STR_ITEM_SUMMON_03_DESC</v>
       </c>
       <c r="F119" s="39">
         <v>4</v>
@@ -16424,7 +16432,7 @@
         <v>438</v>
       </c>
       <c r="Q119" s="39">
-        <v>10020</v>
+        <v>10019</v>
       </c>
       <c r="R119" s="39" t="s">
         <v>41</v>
@@ -16467,21 +16475,21 @@
     </row>
     <row r="120" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A120" s="39">
-        <v>39006</v>
+        <v>39005</v>
       </c>
       <c r="B120" s="40" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="C120" s="41" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="D120" s="39" t="str">
-        <f t="shared" ref="D120" si="62">"STR_"&amp;UPPER(C120)</f>
-        <v>STR_ITEM_SUMMON_05</v>
+        <f t="shared" si="62"/>
+        <v>STR_ITEM_SUMMON_04</v>
       </c>
       <c r="E120" s="39" t="str">
-        <f t="shared" ref="E120" si="63">D120&amp;"_DESC"</f>
-        <v>STR_ITEM_SUMMON_05_DESC</v>
+        <f t="shared" si="63"/>
+        <v>STR_ITEM_SUMMON_04_DESC</v>
       </c>
       <c r="F120" s="39">
         <v>4</v>
@@ -16515,7 +16523,7 @@
         <v>438</v>
       </c>
       <c r="Q120" s="39">
-        <v>10021</v>
+        <v>10020</v>
       </c>
       <c r="R120" s="39" t="s">
         <v>41</v>
@@ -16553,6 +16561,97 @@
         <v>41</v>
       </c>
       <c r="AE120" s="39" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="121" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="A121" s="39">
+        <v>39006</v>
+      </c>
+      <c r="B121" s="40" t="s">
+        <v>449</v>
+      </c>
+      <c r="C121" s="41" t="s">
+        <v>445</v>
+      </c>
+      <c r="D121" s="39" t="str">
+        <f t="shared" ref="D121" si="64">"STR_"&amp;UPPER(C121)</f>
+        <v>STR_ITEM_SUMMON_05</v>
+      </c>
+      <c r="E121" s="39" t="str">
+        <f t="shared" ref="E121" si="65">D121&amp;"_DESC"</f>
+        <v>STR_ITEM_SUMMON_05_DESC</v>
+      </c>
+      <c r="F121" s="39">
+        <v>4</v>
+      </c>
+      <c r="G121" s="39" t="s">
+        <v>48</v>
+      </c>
+      <c r="H121" s="39">
+        <v>0</v>
+      </c>
+      <c r="I121" s="39">
+        <v>0</v>
+      </c>
+      <c r="J121" s="39">
+        <v>0</v>
+      </c>
+      <c r="K121" s="39">
+        <v>0</v>
+      </c>
+      <c r="L121" s="39">
+        <v>0</v>
+      </c>
+      <c r="M121" s="39">
+        <v>0</v>
+      </c>
+      <c r="N121" s="39">
+        <v>0</v>
+      </c>
+      <c r="O121" s="39"/>
+      <c r="P121" s="39" t="s">
+        <v>438</v>
+      </c>
+      <c r="Q121" s="39">
+        <v>10021</v>
+      </c>
+      <c r="R121" s="39" t="s">
+        <v>41</v>
+      </c>
+      <c r="S121" s="39"/>
+      <c r="T121" s="39"/>
+      <c r="U121" s="39" t="s">
+        <v>41</v>
+      </c>
+      <c r="V121" s="39" t="s">
+        <v>41</v>
+      </c>
+      <c r="W121" s="39" t="b">
+        <v>1</v>
+      </c>
+      <c r="X121" s="39">
+        <v>10</v>
+      </c>
+      <c r="Y121" s="39">
+        <v>125</v>
+      </c>
+      <c r="Z121" s="39" t="s">
+        <v>41</v>
+      </c>
+      <c r="AA121" s="39">
+        <v>0</v>
+      </c>
+      <c r="AB121" s="39" t="s">
+        <v>439</v>
+      </c>
+      <c r="AC121" s="39" t="s">
+        <v>41</v>
+      </c>
+      <c r="AD121" s="39" t="s">
+        <v>41</v>
+      </c>
+      <c r="AE121" s="39" t="s">
         <v>41</v>
       </c>
     </row>
@@ -16563,7 +16662,7 @@
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" r:id="rId1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="64">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="65">
         <x14:dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>Definition!#REF!</xm:f>
@@ -16571,19 +16670,16 @@
           <x14:formula2>
             <xm:f>Definition!#REF!</xm:f>
           </x14:formula2>
-          <xm:sqref>F113</xm:sqref>
+          <xm:sqref>F114</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+        <x14:dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
-            <xm:f>Type!$B$2:$B$20</xm:f>
+            <xm:f>Definition!F32</xm:f>
           </x14:formula1>
-          <xm:sqref>P2:P120</xm:sqref>
-        </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
-          <x14:formula1>
-            <xm:f>Type!$A$2:$A$101</xm:f>
-          </x14:formula1>
-          <xm:sqref>G1:G1048576</xm:sqref>
+          <x14:formula2>
+            <xm:f>Definition!G32</xm:f>
+          </x14:formula2>
+          <xm:sqref>F115:F121</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
@@ -16592,16 +16688,7 @@
           <x14:formula2>
             <xm:f>Definition!G35</xm:f>
           </x14:formula2>
-          <xm:sqref>F112</xm:sqref>
-        </x14:dataValidation>
-        <x14:dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1">
-          <x14:formula1>
-            <xm:f>Definition!F32</xm:f>
-          </x14:formula1>
-          <x14:formula2>
-            <xm:f>Definition!G32</xm:f>
-          </x14:formula2>
-          <xm:sqref>F114:F120</xm:sqref>
+          <xm:sqref>F112:F113</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
@@ -16628,7 +16715,16 @@
           <x14:formula2>
             <xm:f>Definition!G31</xm:f>
           </x14:formula2>
-          <xm:sqref>H112:H120</xm:sqref>
+          <xm:sqref>H112:H113</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+          <x14:formula1>
+            <xm:f>Definition!F32</xm:f>
+          </x14:formula1>
+          <x14:formula2>
+            <xm:f>Definition!G32</xm:f>
+          </x14:formula2>
+          <xm:sqref>H114:H121</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
@@ -16709,7 +16805,7 @@
           <x14:formula2>
             <xm:f>Definition!G24</xm:f>
           </x14:formula2>
-          <xm:sqref>F85:F87 F50 F58 F54 F62</xm:sqref>
+          <xm:sqref>F85:F87 F62 F54 F58 F50</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
@@ -16817,7 +16913,7 @@
           <x14:formula2>
             <xm:f>Definition!G34</xm:f>
           </x14:formula2>
-          <xm:sqref>F73:F75 F55:F57 F59:F61 F51:F53</xm:sqref>
+          <xm:sqref>F73:F75 F51:F53 F59:F61 F55:F57</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
@@ -16826,7 +16922,7 @@
           <x14:formula2>
             <xm:f>Definition!G38</xm:f>
           </x14:formula2>
-          <xm:sqref>H73:H75 H57 H61 H53</xm:sqref>
+          <xm:sqref>H73:H75 H53 H61 H57</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
@@ -16889,7 +16985,19 @@
           <x14:formula2>
             <xm:f>Definition!G29</xm:f>
           </x14:formula2>
-          <xm:sqref>H50:H52 H58:H60 H54:H56 H62</xm:sqref>
+          <xm:sqref>H50:H52 H62 H54:H56 H58:H60</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+          <x14:formula1>
+            <xm:f>Type!$B$2:$B$20</xm:f>
+          </x14:formula1>
+          <xm:sqref>P2:P121</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+          <x14:formula1>
+            <xm:f>Type!$A$2:$A$101</xm:f>
+          </x14:formula1>
+          <xm:sqref>G1:G1048576</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>

--- a/30_table/01_테스트버전/Table_Data_Item.xlsx
+++ b/30_table/01_테스트버전/Table_Data_Item.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr codeName="현재_통합_문서" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="-15" yWindow="105" windowWidth="19215" windowHeight="12075" activeTab="2"/>
+    <workbookView xWindow="-15" yWindow="165" windowWidth="19215" windowHeight="12015" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="DOC History" sheetId="6" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1604" uniqueCount="461">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1616" uniqueCount="465">
   <si>
     <t>작업자</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1620,6 +1620,21 @@
   </si>
   <si>
     <t>item_quest_02</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>리비히의 서</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>item_quest_03</t>
+  </si>
+  <si>
+    <t>icon_item_5005</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>icon_item_5006</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -5853,7 +5868,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet3"/>
-  <dimension ref="A1:AE121"/>
+  <dimension ref="A1:AE122"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="6.5" style="37" bestFit="1" customWidth="1"/>
@@ -14766,11 +14781,11 @@
         <v>111</v>
       </c>
       <c r="D100" s="39" t="str">
-        <f t="shared" ref="D100:D115" si="44">"STR_"&amp;UPPER(C100)</f>
+        <f t="shared" ref="D100:D116" si="44">"STR_"&amp;UPPER(C100)</f>
         <v>STR_ITEM_BOX_01</v>
       </c>
       <c r="E100" s="39" t="str">
-        <f t="shared" ref="E100:E115" si="45">D100&amp;"_DESC"</f>
+        <f t="shared" ref="E100:E116" si="45">D100&amp;"_DESC"</f>
         <v>STR_ITEM_BOX_01_DESC</v>
       </c>
       <c r="F100" s="39">
@@ -15858,7 +15873,7 @@
         <v>STR_ITEM_QUEST_02_DESC</v>
       </c>
       <c r="F113" s="39">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G113" s="39" t="s">
         <v>54</v>
@@ -15918,7 +15933,7 @@
         <v>0</v>
       </c>
       <c r="AB113" s="39" t="s">
-        <v>125</v>
+        <v>463</v>
       </c>
       <c r="AC113" s="39" t="s">
         <v>41</v>
@@ -15931,202 +15946,202 @@
       </c>
     </row>
     <row r="114" spans="1:31" x14ac:dyDescent="0.3">
-      <c r="A114" s="34">
+      <c r="A114" s="39">
+        <v>38002</v>
+      </c>
+      <c r="B114" s="40" t="s">
+        <v>461</v>
+      </c>
+      <c r="C114" s="41" t="s">
+        <v>462</v>
+      </c>
+      <c r="D114" s="39" t="str">
+        <f t="shared" ref="D114" si="58">"STR_"&amp;UPPER(C114)</f>
+        <v>STR_ITEM_QUEST_03</v>
+      </c>
+      <c r="E114" s="39" t="str">
+        <f t="shared" ref="E114" si="59">D114&amp;"_DESC"</f>
+        <v>STR_ITEM_QUEST_03_DESC</v>
+      </c>
+      <c r="F114" s="39">
+        <v>6</v>
+      </c>
+      <c r="G114" s="39" t="s">
+        <v>54</v>
+      </c>
+      <c r="H114" s="39">
+        <v>0</v>
+      </c>
+      <c r="I114" s="39">
+        <v>0</v>
+      </c>
+      <c r="J114" s="39">
+        <v>0</v>
+      </c>
+      <c r="K114" s="39">
+        <v>0</v>
+      </c>
+      <c r="L114" s="39">
+        <v>0</v>
+      </c>
+      <c r="M114" s="39">
+        <v>0</v>
+      </c>
+      <c r="N114" s="39">
+        <v>0</v>
+      </c>
+      <c r="O114" s="39"/>
+      <c r="P114" s="39" t="s">
+        <v>44</v>
+      </c>
+      <c r="Q114" s="39">
+        <v>0</v>
+      </c>
+      <c r="R114" s="39" t="s">
+        <v>41</v>
+      </c>
+      <c r="S114" s="39"/>
+      <c r="T114" s="39"/>
+      <c r="U114" s="39" t="s">
+        <v>41</v>
+      </c>
+      <c r="V114" s="39" t="s">
+        <v>41</v>
+      </c>
+      <c r="W114" s="39" t="b">
+        <v>0</v>
+      </c>
+      <c r="X114" s="39">
+        <v>10</v>
+      </c>
+      <c r="Y114" s="39">
+        <v>0</v>
+      </c>
+      <c r="Z114" s="39" t="s">
+        <v>41</v>
+      </c>
+      <c r="AA114" s="39">
+        <v>0</v>
+      </c>
+      <c r="AB114" s="39" t="s">
+        <v>464</v>
+      </c>
+      <c r="AC114" s="39" t="s">
+        <v>41</v>
+      </c>
+      <c r="AD114" s="39" t="s">
+        <v>41</v>
+      </c>
+      <c r="AE114" s="39" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="115" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="A115" s="34">
         <v>38500</v>
       </c>
-      <c r="B114" s="35" t="s">
+      <c r="B115" s="35" t="s">
         <v>171</v>
       </c>
-      <c r="C114" s="36" t="s">
+      <c r="C115" s="36" t="s">
         <v>113</v>
       </c>
-      <c r="D114" s="34" t="str">
+      <c r="D115" s="34" t="str">
         <f t="shared" si="44"/>
         <v>STR_ITEM_METERIAL_01</v>
       </c>
-      <c r="E114" s="34" t="str">
+      <c r="E115" s="34" t="str">
         <f t="shared" si="45"/>
         <v>STR_ITEM_METERIAL_01_DESC</v>
       </c>
-      <c r="F114" s="34">
-        <v>0</v>
-      </c>
-      <c r="G114" s="34" t="s">
+      <c r="F115" s="34">
+        <v>0</v>
+      </c>
+      <c r="G115" s="34" t="s">
         <v>56</v>
       </c>
-      <c r="H114" s="34">
-        <v>0</v>
-      </c>
-      <c r="I114" s="34">
-        <v>0</v>
-      </c>
-      <c r="J114" s="34">
-        <v>0</v>
-      </c>
-      <c r="K114" s="34">
-        <v>0</v>
-      </c>
-      <c r="L114" s="34">
-        <v>0</v>
-      </c>
-      <c r="M114" s="34">
-        <v>0</v>
-      </c>
-      <c r="N114" s="34">
-        <v>0</v>
-      </c>
-      <c r="P114" s="34" t="s">
+      <c r="H115" s="34">
+        <v>0</v>
+      </c>
+      <c r="I115" s="34">
+        <v>0</v>
+      </c>
+      <c r="J115" s="34">
+        <v>0</v>
+      </c>
+      <c r="K115" s="34">
+        <v>0</v>
+      </c>
+      <c r="L115" s="34">
+        <v>0</v>
+      </c>
+      <c r="M115" s="34">
+        <v>0</v>
+      </c>
+      <c r="N115" s="34">
+        <v>0</v>
+      </c>
+      <c r="P115" s="34" t="s">
         <v>44</v>
       </c>
-      <c r="Q114" s="34">
-        <v>0</v>
-      </c>
-      <c r="R114" s="37" t="s">
-        <v>41</v>
-      </c>
-      <c r="U114" s="37" t="s">
-        <v>41</v>
-      </c>
-      <c r="V114" s="37" t="s">
-        <v>41</v>
-      </c>
-      <c r="W114" s="34" t="b">
+      <c r="Q115" s="34">
+        <v>0</v>
+      </c>
+      <c r="R115" s="37" t="s">
+        <v>41</v>
+      </c>
+      <c r="U115" s="37" t="s">
+        <v>41</v>
+      </c>
+      <c r="V115" s="37" t="s">
+        <v>41</v>
+      </c>
+      <c r="W115" s="34" t="b">
         <v>1</v>
       </c>
-      <c r="X114" s="34">
+      <c r="X115" s="34">
         <v>10</v>
       </c>
-      <c r="Y114" s="34">
-        <v>0</v>
-      </c>
-      <c r="Z114" s="34" t="s">
-        <v>41</v>
-      </c>
-      <c r="AA114" s="37">
-        <v>0</v>
-      </c>
-      <c r="AB114" s="37" t="s">
+      <c r="Y115" s="34">
+        <v>0</v>
+      </c>
+      <c r="Z115" s="34" t="s">
+        <v>41</v>
+      </c>
+      <c r="AA115" s="37">
+        <v>0</v>
+      </c>
+      <c r="AB115" s="37" t="s">
         <v>125</v>
       </c>
-      <c r="AC114" s="37" t="s">
-        <v>41</v>
-      </c>
-      <c r="AD114" s="37" t="s">
-        <v>41</v>
-      </c>
-      <c r="AE114" s="37" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="115" spans="1:31" x14ac:dyDescent="0.3">
-      <c r="A115" s="39">
+      <c r="AC115" s="37" t="s">
+        <v>41</v>
+      </c>
+      <c r="AD115" s="37" t="s">
+        <v>41</v>
+      </c>
+      <c r="AE115" s="37" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="116" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="A116" s="39">
         <v>39000</v>
       </c>
-      <c r="B115" s="40" t="s">
+      <c r="B116" s="40" t="s">
         <v>172</v>
       </c>
-      <c r="C115" s="41" t="s">
+      <c r="C116" s="41" t="s">
         <v>162</v>
       </c>
-      <c r="D115" s="39" t="str">
+      <c r="D116" s="39" t="str">
         <f t="shared" si="44"/>
         <v>STR_ITEM_POTION_ITEMSLOT_01</v>
       </c>
-      <c r="E115" s="39" t="str">
+      <c r="E116" s="39" t="str">
         <f t="shared" si="45"/>
         <v>STR_ITEM_POTION_ITEMSLOT_01_DESC</v>
       </c>
-      <c r="F115" s="39">
-        <v>0</v>
-      </c>
-      <c r="G115" s="39" t="s">
-        <v>48</v>
-      </c>
-      <c r="H115" s="39">
-        <v>0</v>
-      </c>
-      <c r="I115" s="39">
-        <v>0</v>
-      </c>
-      <c r="J115" s="39">
-        <v>0</v>
-      </c>
-      <c r="K115" s="39">
-        <v>0</v>
-      </c>
-      <c r="L115" s="39">
-        <v>0</v>
-      </c>
-      <c r="M115" s="39">
-        <v>0</v>
-      </c>
-      <c r="N115" s="39">
-        <v>0</v>
-      </c>
-      <c r="O115" s="39"/>
-      <c r="P115" s="39" t="s">
-        <v>163</v>
-      </c>
-      <c r="Q115" s="39">
-        <v>5</v>
-      </c>
-      <c r="R115" s="39" t="s">
-        <v>41</v>
-      </c>
-      <c r="S115" s="39"/>
-      <c r="T115" s="39"/>
-      <c r="U115" s="39" t="s">
-        <v>41</v>
-      </c>
-      <c r="V115" s="39" t="s">
-        <v>41</v>
-      </c>
-      <c r="W115" s="39" t="b">
-        <v>1</v>
-      </c>
-      <c r="X115" s="39">
-        <v>10</v>
-      </c>
-      <c r="Y115" s="39">
-        <v>25</v>
-      </c>
-      <c r="Z115" s="39" t="s">
-        <v>41</v>
-      </c>
-      <c r="AA115" s="39">
-        <v>0</v>
-      </c>
-      <c r="AB115" s="39" t="s">
-        <v>302</v>
-      </c>
-      <c r="AC115" s="39" t="s">
-        <v>41</v>
-      </c>
-      <c r="AD115" s="39" t="s">
-        <v>41</v>
-      </c>
-      <c r="AE115" s="39" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="116" spans="1:31" x14ac:dyDescent="0.3">
-      <c r="A116" s="39">
-        <v>39001</v>
-      </c>
-      <c r="B116" s="40" t="s">
-        <v>173</v>
-      </c>
-      <c r="C116" s="41" t="s">
-        <v>166</v>
-      </c>
-      <c r="D116" s="39" t="str">
-        <f t="shared" ref="D116" si="58">"STR_"&amp;UPPER(C116)</f>
-        <v>STR_ITEM_POTION_SLOT_01</v>
-      </c>
-      <c r="E116" s="39" t="str">
-        <f t="shared" ref="E116" si="59">D116&amp;"_DESC"</f>
-        <v>STR_ITEM_POTION_SLOT_01_DESC</v>
-      </c>
       <c r="F116" s="39">
         <v>0</v>
       </c>
@@ -16156,10 +16171,10 @@
       </c>
       <c r="O116" s="39"/>
       <c r="P116" s="39" t="s">
-        <v>263</v>
+        <v>163</v>
       </c>
       <c r="Q116" s="39">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="R116" s="39" t="s">
         <v>41</v>
@@ -16179,7 +16194,7 @@
         <v>10</v>
       </c>
       <c r="Y116" s="39">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="Z116" s="39" t="s">
         <v>41</v>
@@ -16188,7 +16203,7 @@
         <v>0</v>
       </c>
       <c r="AB116" s="39" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="AC116" s="39" t="s">
         <v>41</v>
@@ -16202,24 +16217,24 @@
     </row>
     <row r="117" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A117" s="39">
-        <v>39002</v>
+        <v>39001</v>
       </c>
       <c r="B117" s="40" t="s">
-        <v>440</v>
+        <v>173</v>
       </c>
       <c r="C117" s="41" t="s">
-        <v>437</v>
+        <v>166</v>
       </c>
       <c r="D117" s="39" t="str">
         <f t="shared" ref="D117" si="60">"STR_"&amp;UPPER(C117)</f>
-        <v>STR_ITEM_SUMMON_01</v>
+        <v>STR_ITEM_POTION_SLOT_01</v>
       </c>
       <c r="E117" s="39" t="str">
         <f t="shared" ref="E117" si="61">D117&amp;"_DESC"</f>
-        <v>STR_ITEM_SUMMON_01_DESC</v>
+        <v>STR_ITEM_POTION_SLOT_01_DESC</v>
       </c>
       <c r="F117" s="39">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G117" s="39" t="s">
         <v>48</v>
@@ -16247,10 +16262,10 @@
       </c>
       <c r="O117" s="39"/>
       <c r="P117" s="39" t="s">
-        <v>438</v>
+        <v>263</v>
       </c>
       <c r="Q117" s="39">
-        <v>10017</v>
+        <v>1</v>
       </c>
       <c r="R117" s="39" t="s">
         <v>41</v>
@@ -16270,7 +16285,7 @@
         <v>10</v>
       </c>
       <c r="Y117" s="39">
-        <v>125</v>
+        <v>50</v>
       </c>
       <c r="Z117" s="39" t="s">
         <v>41</v>
@@ -16279,7 +16294,7 @@
         <v>0</v>
       </c>
       <c r="AB117" s="39" t="s">
-        <v>439</v>
+        <v>303</v>
       </c>
       <c r="AC117" s="39" t="s">
         <v>41</v>
@@ -16293,21 +16308,21 @@
     </row>
     <row r="118" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A118" s="39">
-        <v>39003</v>
+        <v>39002</v>
       </c>
       <c r="B118" s="40" t="s">
-        <v>446</v>
+        <v>440</v>
       </c>
       <c r="C118" s="41" t="s">
-        <v>442</v>
+        <v>437</v>
       </c>
       <c r="D118" s="39" t="str">
-        <f t="shared" ref="D118:D120" si="62">"STR_"&amp;UPPER(C118)</f>
-        <v>STR_ITEM_SUMMON_02</v>
+        <f t="shared" ref="D118" si="62">"STR_"&amp;UPPER(C118)</f>
+        <v>STR_ITEM_SUMMON_01</v>
       </c>
       <c r="E118" s="39" t="str">
-        <f t="shared" ref="E118:E120" si="63">D118&amp;"_DESC"</f>
-        <v>STR_ITEM_SUMMON_02_DESC</v>
+        <f t="shared" ref="E118" si="63">D118&amp;"_DESC"</f>
+        <v>STR_ITEM_SUMMON_01_DESC</v>
       </c>
       <c r="F118" s="39">
         <v>4</v>
@@ -16341,7 +16356,7 @@
         <v>438</v>
       </c>
       <c r="Q118" s="39">
-        <v>10018</v>
+        <v>10017</v>
       </c>
       <c r="R118" s="39" t="s">
         <v>41</v>
@@ -16384,21 +16399,21 @@
     </row>
     <row r="119" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A119" s="39">
-        <v>39004</v>
+        <v>39003</v>
       </c>
       <c r="B119" s="40" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="C119" s="41" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="D119" s="39" t="str">
-        <f t="shared" si="62"/>
-        <v>STR_ITEM_SUMMON_03</v>
+        <f t="shared" ref="D119:D121" si="64">"STR_"&amp;UPPER(C119)</f>
+        <v>STR_ITEM_SUMMON_02</v>
       </c>
       <c r="E119" s="39" t="str">
-        <f t="shared" si="63"/>
-        <v>STR_ITEM_SUMMON_03_DESC</v>
+        <f t="shared" ref="E119:E121" si="65">D119&amp;"_DESC"</f>
+        <v>STR_ITEM_SUMMON_02_DESC</v>
       </c>
       <c r="F119" s="39">
         <v>4</v>
@@ -16432,7 +16447,7 @@
         <v>438</v>
       </c>
       <c r="Q119" s="39">
-        <v>10019</v>
+        <v>10018</v>
       </c>
       <c r="R119" s="39" t="s">
         <v>41</v>
@@ -16475,21 +16490,21 @@
     </row>
     <row r="120" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A120" s="39">
-        <v>39005</v>
+        <v>39004</v>
       </c>
       <c r="B120" s="40" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="C120" s="41" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="D120" s="39" t="str">
-        <f t="shared" si="62"/>
-        <v>STR_ITEM_SUMMON_04</v>
+        <f t="shared" si="64"/>
+        <v>STR_ITEM_SUMMON_03</v>
       </c>
       <c r="E120" s="39" t="str">
-        <f t="shared" si="63"/>
-        <v>STR_ITEM_SUMMON_04_DESC</v>
+        <f t="shared" si="65"/>
+        <v>STR_ITEM_SUMMON_03_DESC</v>
       </c>
       <c r="F120" s="39">
         <v>4</v>
@@ -16523,7 +16538,7 @@
         <v>438</v>
       </c>
       <c r="Q120" s="39">
-        <v>10020</v>
+        <v>10019</v>
       </c>
       <c r="R120" s="39" t="s">
         <v>41</v>
@@ -16566,21 +16581,21 @@
     </row>
     <row r="121" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A121" s="39">
-        <v>39006</v>
+        <v>39005</v>
       </c>
       <c r="B121" s="40" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="C121" s="41" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="D121" s="39" t="str">
-        <f t="shared" ref="D121" si="64">"STR_"&amp;UPPER(C121)</f>
-        <v>STR_ITEM_SUMMON_05</v>
+        <f t="shared" si="64"/>
+        <v>STR_ITEM_SUMMON_04</v>
       </c>
       <c r="E121" s="39" t="str">
-        <f t="shared" ref="E121" si="65">D121&amp;"_DESC"</f>
-        <v>STR_ITEM_SUMMON_05_DESC</v>
+        <f t="shared" si="65"/>
+        <v>STR_ITEM_SUMMON_04_DESC</v>
       </c>
       <c r="F121" s="39">
         <v>4</v>
@@ -16614,7 +16629,7 @@
         <v>438</v>
       </c>
       <c r="Q121" s="39">
-        <v>10021</v>
+        <v>10020</v>
       </c>
       <c r="R121" s="39" t="s">
         <v>41</v>
@@ -16652,6 +16667,97 @@
         <v>41</v>
       </c>
       <c r="AE121" s="39" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="122" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="A122" s="39">
+        <v>39006</v>
+      </c>
+      <c r="B122" s="40" t="s">
+        <v>449</v>
+      </c>
+      <c r="C122" s="41" t="s">
+        <v>445</v>
+      </c>
+      <c r="D122" s="39" t="str">
+        <f t="shared" ref="D122" si="66">"STR_"&amp;UPPER(C122)</f>
+        <v>STR_ITEM_SUMMON_05</v>
+      </c>
+      <c r="E122" s="39" t="str">
+        <f t="shared" ref="E122" si="67">D122&amp;"_DESC"</f>
+        <v>STR_ITEM_SUMMON_05_DESC</v>
+      </c>
+      <c r="F122" s="39">
+        <v>4</v>
+      </c>
+      <c r="G122" s="39" t="s">
+        <v>48</v>
+      </c>
+      <c r="H122" s="39">
+        <v>0</v>
+      </c>
+      <c r="I122" s="39">
+        <v>0</v>
+      </c>
+      <c r="J122" s="39">
+        <v>0</v>
+      </c>
+      <c r="K122" s="39">
+        <v>0</v>
+      </c>
+      <c r="L122" s="39">
+        <v>0</v>
+      </c>
+      <c r="M122" s="39">
+        <v>0</v>
+      </c>
+      <c r="N122" s="39">
+        <v>0</v>
+      </c>
+      <c r="O122" s="39"/>
+      <c r="P122" s="39" t="s">
+        <v>438</v>
+      </c>
+      <c r="Q122" s="39">
+        <v>10021</v>
+      </c>
+      <c r="R122" s="39" t="s">
+        <v>41</v>
+      </c>
+      <c r="S122" s="39"/>
+      <c r="T122" s="39"/>
+      <c r="U122" s="39" t="s">
+        <v>41</v>
+      </c>
+      <c r="V122" s="39" t="s">
+        <v>41</v>
+      </c>
+      <c r="W122" s="39" t="b">
+        <v>1</v>
+      </c>
+      <c r="X122" s="39">
+        <v>10</v>
+      </c>
+      <c r="Y122" s="39">
+        <v>125</v>
+      </c>
+      <c r="Z122" s="39" t="s">
+        <v>41</v>
+      </c>
+      <c r="AA122" s="39">
+        <v>0</v>
+      </c>
+      <c r="AB122" s="39" t="s">
+        <v>439</v>
+      </c>
+      <c r="AC122" s="39" t="s">
+        <v>41</v>
+      </c>
+      <c r="AD122" s="39" t="s">
+        <v>41</v>
+      </c>
+      <c r="AE122" s="39" t="s">
         <v>41</v>
       </c>
     </row>
@@ -16670,7 +16776,7 @@
           <x14:formula2>
             <xm:f>Definition!#REF!</xm:f>
           </x14:formula2>
-          <xm:sqref>F114</xm:sqref>
+          <xm:sqref>F115</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
@@ -16679,7 +16785,28 @@
           <x14:formula2>
             <xm:f>Definition!G32</xm:f>
           </x14:formula2>
-          <xm:sqref>F115:F121</xm:sqref>
+          <xm:sqref>F116:F122</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+          <x14:formula1>
+            <xm:f>Definition!F32</xm:f>
+          </x14:formula1>
+          <x14:formula2>
+            <xm:f>Definition!G32</xm:f>
+          </x14:formula2>
+          <xm:sqref>H115:H122</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+          <x14:formula1>
+            <xm:f>Type!$B$2:$B$20</xm:f>
+          </x14:formula1>
+          <xm:sqref>P2:P122</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+          <x14:formula1>
+            <xm:f>Type!$A$2:$A$101</xm:f>
+          </x14:formula1>
+          <xm:sqref>G1:G1048576</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
@@ -16688,7 +16815,7 @@
           <x14:formula2>
             <xm:f>Definition!G35</xm:f>
           </x14:formula2>
-          <xm:sqref>F112:F113</xm:sqref>
+          <xm:sqref>F112:F114</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
@@ -16715,16 +16842,7 @@
           <x14:formula2>
             <xm:f>Definition!G31</xm:f>
           </x14:formula2>
-          <xm:sqref>H112:H113</xm:sqref>
-        </x14:dataValidation>
-        <x14:dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1">
-          <x14:formula1>
-            <xm:f>Definition!F32</xm:f>
-          </x14:formula1>
-          <x14:formula2>
-            <xm:f>Definition!G32</xm:f>
-          </x14:formula2>
-          <xm:sqref>H114:H121</xm:sqref>
+          <xm:sqref>H112:H114</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
@@ -16805,7 +16923,7 @@
           <x14:formula2>
             <xm:f>Definition!G24</xm:f>
           </x14:formula2>
-          <xm:sqref>F85:F87 F62 F54 F58 F50</xm:sqref>
+          <xm:sqref>F85:F87 F50 F58 F54 F62</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
@@ -16913,7 +17031,7 @@
           <x14:formula2>
             <xm:f>Definition!G34</xm:f>
           </x14:formula2>
-          <xm:sqref>F73:F75 F51:F53 F59:F61 F55:F57</xm:sqref>
+          <xm:sqref>F73:F75 F55:F57 F59:F61 F51:F53</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
@@ -16922,7 +17040,7 @@
           <x14:formula2>
             <xm:f>Definition!G38</xm:f>
           </x14:formula2>
-          <xm:sqref>H73:H75 H53 H61 H57</xm:sqref>
+          <xm:sqref>H73:H75 H57 H61 H53</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
@@ -16985,19 +17103,7 @@
           <x14:formula2>
             <xm:f>Definition!G29</xm:f>
           </x14:formula2>
-          <xm:sqref>H50:H52 H62 H54:H56 H58:H60</xm:sqref>
-        </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
-          <x14:formula1>
-            <xm:f>Type!$B$2:$B$20</xm:f>
-          </x14:formula1>
-          <xm:sqref>P2:P121</xm:sqref>
-        </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
-          <x14:formula1>
-            <xm:f>Type!$A$2:$A$101</xm:f>
-          </x14:formula1>
-          <xm:sqref>G1:G1048576</xm:sqref>
+          <xm:sqref>H50:H52 H58:H60 H54:H56 H62</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>

--- a/30_table/01_테스트버전/Table_Data_Item.xlsx
+++ b/30_table/01_테스트버전/Table_Data_Item.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1616" uniqueCount="465">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1616" uniqueCount="479">
   <si>
     <t>작업자</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1635,6 +1635,53 @@
   </si>
   <si>
     <t>icon_item_5006</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>icon_item_3004</t>
+  </si>
+  <si>
+    <t>icon_item_3005</t>
+  </si>
+  <si>
+    <t>icon_item_3006</t>
+  </si>
+  <si>
+    <t>icon_item_3007</t>
+  </si>
+  <si>
+    <t>icon_item_3008</t>
+  </si>
+  <si>
+    <t>icon_item_3009</t>
+  </si>
+  <si>
+    <t>icon_item_3010</t>
+  </si>
+  <si>
+    <t>icon_item_3011</t>
+  </si>
+  <si>
+    <t>icon_item_3012</t>
+  </si>
+  <si>
+    <t>icon_item_2009</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>icon_item_2003</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>icon_item_2008</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>icon_item_2004</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>icon_item_2007</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -9435,7 +9482,7 @@
         <v>0</v>
       </c>
       <c r="AB39" s="37" t="s">
-        <v>285</v>
+        <v>474</v>
       </c>
       <c r="AC39" s="37" t="s">
         <v>41</v>
@@ -9523,7 +9570,7 @@
         <v>0</v>
       </c>
       <c r="AB40" s="37" t="s">
-        <v>286</v>
+        <v>475</v>
       </c>
       <c r="AC40" s="37" t="s">
         <v>41</v>
@@ -9617,7 +9664,7 @@
         <v>0</v>
       </c>
       <c r="AB41" s="37" t="s">
-        <v>287</v>
+        <v>477</v>
       </c>
       <c r="AC41" s="37" t="s">
         <v>41</v>
@@ -9705,7 +9752,7 @@
         <v>0</v>
       </c>
       <c r="AB42" s="37" t="s">
-        <v>285</v>
+        <v>476</v>
       </c>
       <c r="AC42" s="37" t="s">
         <v>41</v>
@@ -9793,7 +9840,7 @@
         <v>0</v>
       </c>
       <c r="AB43" s="37" t="s">
-        <v>286</v>
+        <v>478</v>
       </c>
       <c r="AC43" s="37" t="s">
         <v>41</v>
@@ -9887,7 +9934,7 @@
         <v>0</v>
       </c>
       <c r="AB44" s="37" t="s">
-        <v>287</v>
+        <v>474</v>
       </c>
       <c r="AC44" s="37" t="s">
         <v>41</v>
@@ -10816,7 +10863,7 @@
         <v>0</v>
       </c>
       <c r="AB54" s="39" t="s">
-        <v>288</v>
+        <v>465</v>
       </c>
       <c r="AC54" s="39" t="s">
         <v>41</v>
@@ -10907,7 +10954,7 @@
         <v>0</v>
       </c>
       <c r="AB55" s="39" t="s">
-        <v>289</v>
+        <v>466</v>
       </c>
       <c r="AC55" s="39" t="s">
         <v>41</v>
@@ -11002,7 +11049,7 @@
         <v>0</v>
       </c>
       <c r="AB56" s="39" t="s">
-        <v>290</v>
+        <v>467</v>
       </c>
       <c r="AC56" s="39" t="s">
         <v>41</v>
@@ -11087,7 +11134,7 @@
         <v>0</v>
       </c>
       <c r="AB57" s="39" t="s">
-        <v>288</v>
+        <v>468</v>
       </c>
       <c r="AC57" s="39" t="s">
         <v>41</v>
@@ -11178,7 +11225,7 @@
         <v>0</v>
       </c>
       <c r="AB58" s="39" t="s">
-        <v>289</v>
+        <v>469</v>
       </c>
       <c r="AC58" s="39" t="s">
         <v>41</v>
@@ -11273,7 +11320,7 @@
         <v>0</v>
       </c>
       <c r="AB59" s="39" t="s">
-        <v>290</v>
+        <v>470</v>
       </c>
       <c r="AC59" s="39" t="s">
         <v>41</v>
@@ -11364,7 +11411,7 @@
         <v>0</v>
       </c>
       <c r="AB60" s="39" t="s">
-        <v>288</v>
+        <v>471</v>
       </c>
       <c r="AC60" s="39" t="s">
         <v>41</v>
@@ -11449,7 +11496,7 @@
         <v>0</v>
       </c>
       <c r="AB61" s="39" t="s">
-        <v>289</v>
+        <v>472</v>
       </c>
       <c r="AC61" s="39" t="s">
         <v>41</v>
@@ -11544,7 +11591,7 @@
         <v>0</v>
       </c>
       <c r="AB62" s="39" t="s">
-        <v>290</v>
+        <v>473</v>
       </c>
       <c r="AC62" s="39" t="s">
         <v>41</v>

--- a/30_table/01_테스트버전/Table_Data_Item.xlsx
+++ b/30_table/01_테스트버전/Table_Data_Item.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1616" uniqueCount="479">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1652" uniqueCount="517">
   <si>
     <t>작업자</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1174,514 +1174,643 @@
     <t>순금 반지</t>
   </si>
   <si>
-    <t>붉은 마법 반지</t>
+    <t>혈석 반지</t>
+  </si>
+  <si>
+    <t>낡은 신발</t>
+  </si>
+  <si>
+    <t>가죽 신발</t>
+  </si>
+  <si>
+    <t>나무 신발</t>
+  </si>
+  <si>
+    <t>황동 신발</t>
+  </si>
+  <si>
+    <t>철 신발</t>
+  </si>
+  <si>
+    <t>나무 막대기</t>
+  </si>
+  <si>
+    <t>장검</t>
+  </si>
+  <si>
+    <t>주목 지팡이</t>
+  </si>
+  <si>
+    <t>악몽의 지팡이</t>
+  </si>
+  <si>
+    <t>지옥의 지팡이</t>
+  </si>
+  <si>
+    <t>불지옥 지팡이</t>
+  </si>
+  <si>
+    <t>뼈 지팡이</t>
+  </si>
+  <si>
+    <t>전투 지팡이</t>
+  </si>
+  <si>
+    <t>전쟁 지팡이</t>
+  </si>
+  <si>
+    <t>주술 지팡이</t>
+  </si>
+  <si>
+    <t>칠흑 지팡이</t>
+  </si>
+  <si>
+    <t>대장로의 지팡이</t>
+  </si>
+  <si>
+    <t>넓은 검</t>
+  </si>
+  <si>
+    <t>전쟁 검</t>
+  </si>
+  <si>
+    <t>용병 검</t>
+  </si>
+  <si>
+    <t>기사 검</t>
+  </si>
+  <si>
+    <t>검투사 검</t>
+  </si>
+  <si>
+    <t>해적 검</t>
+  </si>
+  <si>
+    <t>제국 검</t>
+  </si>
+  <si>
+    <t>단도</t>
+  </si>
+  <si>
+    <t>비수</t>
+  </si>
+  <si>
+    <t>뿔 단도</t>
+  </si>
+  <si>
+    <t>톱날 단도</t>
+  </si>
+  <si>
+    <t>강철 단도</t>
+  </si>
+  <si>
+    <t>굴절 단도</t>
+  </si>
+  <si>
+    <t>크리스</t>
+  </si>
+  <si>
+    <t>아수라</t>
+  </si>
+  <si>
+    <t>룬 단검</t>
+  </si>
+  <si>
+    <t>소울 브링거</t>
+  </si>
+  <si>
+    <t>흑철 단검</t>
+  </si>
+  <si>
+    <t>그람</t>
+  </si>
+  <si>
+    <t>담로</t>
+  </si>
+  <si>
+    <t>듀랜달</t>
+  </si>
+  <si>
+    <t>막 아 루인</t>
+  </si>
+  <si>
+    <t>리딜</t>
+  </si>
+  <si>
+    <t>나무 장화</t>
+  </si>
+  <si>
+    <t>강화 나무 장화</t>
+  </si>
+  <si>
+    <t>가죽 장화</t>
+  </si>
+  <si>
+    <t>강화 가죽 장화</t>
+  </si>
+  <si>
+    <t>황동 장화</t>
+  </si>
+  <si>
+    <t>강화 황동 장화</t>
+  </si>
+  <si>
+    <t>철 장화</t>
+  </si>
+  <si>
+    <t>강화 철 장화</t>
+  </si>
+  <si>
+    <t>낡은 옷</t>
+  </si>
+  <si>
+    <t>천 옷</t>
+  </si>
+  <si>
+    <t>강화 천 옷</t>
+  </si>
+  <si>
+    <t>레어 천 옷</t>
+  </si>
+  <si>
+    <t>가죽 옷</t>
+  </si>
+  <si>
+    <t>강화 가죽 옷</t>
+  </si>
+  <si>
+    <t>레어 가죽 옷</t>
+  </si>
+  <si>
+    <t>법사 옷</t>
+  </si>
+  <si>
+    <t>장식된 법사 옷</t>
+  </si>
+  <si>
+    <t>레어 법사 옷</t>
+  </si>
+  <si>
+    <t>가죽 갑옷</t>
+  </si>
+  <si>
+    <t>강화 가죽 갑옷</t>
+  </si>
+  <si>
+    <t>레어 가죽 갑옷</t>
+  </si>
+  <si>
+    <t>미션 보상 무기 상자 01</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>item_box_02</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>drop_0023</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>drop_0024</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>미션 보상 갑옷 상자 01</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>item_box_03</t>
+  </si>
+  <si>
+    <t>미션 보상 갑옷 상자 02</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>item_box_04</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>drop_0025</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>item_equip_n_ar_01</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>item_equip_n_ac_01</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>item_equip_n_bo_01</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ADD_ITEM</t>
+  </si>
+  <si>
+    <t>ADD_ITEM</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>금열쇠</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>item_key_03</t>
+  </si>
+  <si>
+    <t>잠겨있는 구리 상자</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>잠겨있는 은 상자</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>잠겨있는 금 상자</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>item_box_05</t>
+  </si>
+  <si>
+    <t>item_box_06</t>
+  </si>
+  <si>
+    <t>item_box_07</t>
+  </si>
+  <si>
+    <t>item_key_01</t>
+  </si>
+  <si>
+    <t>탄환</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Bullet</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>발사체 이름</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Bullet</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>pf_fire_02</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>pf_blade_01</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>pf_dagger_02</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>pf_blade_04</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>pf_fire_01</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>pf_dagger_01</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>pf_blade_05</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>pf_blade_02</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>pf_ice_01</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>pf_dagger_03</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>pf_water_03</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>pf_water_01</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>출석 보상 A등급 캐릭터 상자 01</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>item_box_08</t>
+  </si>
+  <si>
+    <t>item_summon_01</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SUMMON</t>
+  </si>
+  <si>
+    <t>icon_item_9002</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>패트릭 소환권</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>drop_0026</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>item_summon_02</t>
+  </si>
+  <si>
+    <t>item_summon_03</t>
+  </si>
+  <si>
+    <t>item_summon_04</t>
+  </si>
+  <si>
+    <t>item_summon_05</t>
+  </si>
+  <si>
+    <t>앤드류 소환권</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>바르반 바르반</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>헤르미나 소환권</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>카네키 소환권</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>조르의 반지</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>item_equip_r_ac_01</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>item_equip_r_ac_02</t>
+  </si>
+  <si>
+    <t>item_equip_r_ac_03</t>
+  </si>
+  <si>
+    <t>item_equip_r_ac_04</t>
+  </si>
+  <si>
+    <t>item_equip_r_ac_05</t>
+  </si>
+  <si>
+    <t>조르의 보석함</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>item_box_09</t>
+  </si>
+  <si>
+    <t>drop_0027</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>좀비의 영혼</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>item_quest_02</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>리비히의 서</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>item_quest_03</t>
+  </si>
+  <si>
+    <t>icon_item_5005</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>icon_item_5006</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>icon_item_3004</t>
+  </si>
+  <si>
+    <t>icon_item_3005</t>
+  </si>
+  <si>
+    <t>icon_item_3006</t>
+  </si>
+  <si>
+    <t>icon_item_3007</t>
+  </si>
+  <si>
+    <t>icon_item_3008</t>
+  </si>
+  <si>
+    <t>icon_item_3009</t>
+  </si>
+  <si>
+    <t>icon_item_3010</t>
+  </si>
+  <si>
+    <t>icon_item_3011</t>
+  </si>
+  <si>
+    <t>icon_item_3012</t>
+  </si>
+  <si>
+    <t>icon_item_2007</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>마력 반지</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>마나 반지</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>에메랄드 반지</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>루비 반지</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>현자의 반지</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>icon_item_2013</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>icon_item_2014</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>icon_item_2008</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>icon_item_2012</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>icon_item_2009</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>사파이어 반지</t>
-  </si>
-  <si>
-    <t>루비 반지</t>
-  </si>
-  <si>
-    <t>푸른 마법 반지</t>
-  </si>
-  <si>
-    <t>에메랄드 반지</t>
-  </si>
-  <si>
-    <t>혈석 반지</t>
-  </si>
-  <si>
-    <t>달의 반지</t>
-  </si>
-  <si>
-    <t>낡은 신발</t>
-  </si>
-  <si>
-    <t>가죽 신발</t>
-  </si>
-  <si>
-    <t>나무 신발</t>
-  </si>
-  <si>
-    <t>황동 신발</t>
-  </si>
-  <si>
-    <t>철 신발</t>
-  </si>
-  <si>
-    <t>나무 막대기</t>
-  </si>
-  <si>
-    <t>장검</t>
-  </si>
-  <si>
-    <t>주목 지팡이</t>
-  </si>
-  <si>
-    <t>악몽의 지팡이</t>
-  </si>
-  <si>
-    <t>지옥의 지팡이</t>
-  </si>
-  <si>
-    <t>불지옥 지팡이</t>
-  </si>
-  <si>
-    <t>뼈 지팡이</t>
-  </si>
-  <si>
-    <t>전투 지팡이</t>
-  </si>
-  <si>
-    <t>전쟁 지팡이</t>
-  </si>
-  <si>
-    <t>흑요석 지팡이</t>
-  </si>
-  <si>
-    <t>주술 지팡이</t>
-  </si>
-  <si>
-    <t>칠흑 지팡이</t>
-  </si>
-  <si>
-    <t>대장로의 지팡이</t>
-  </si>
-  <si>
-    <t>넓은 검</t>
-  </si>
-  <si>
-    <t>전쟁 검</t>
-  </si>
-  <si>
-    <t>용병 검</t>
-  </si>
-  <si>
-    <t>기사 검</t>
-  </si>
-  <si>
-    <t>검투사 검</t>
-  </si>
-  <si>
-    <t>해적 검</t>
-  </si>
-  <si>
-    <t>제국 검</t>
-  </si>
-  <si>
-    <t>단도</t>
-  </si>
-  <si>
-    <t>비수</t>
-  </si>
-  <si>
-    <t>뿔 단도</t>
-  </si>
-  <si>
-    <t>톱날 단도</t>
-  </si>
-  <si>
-    <t>강철 단도</t>
-  </si>
-  <si>
-    <t>굴절 단도</t>
-  </si>
-  <si>
-    <t>크리스</t>
-  </si>
-  <si>
-    <t>아수라</t>
-  </si>
-  <si>
-    <t>룬 단검</t>
-  </si>
-  <si>
-    <t>소울 브링거</t>
-  </si>
-  <si>
-    <t>흑철 단검</t>
-  </si>
-  <si>
-    <t>그람</t>
-  </si>
-  <si>
-    <t>담로</t>
-  </si>
-  <si>
-    <t>듀랜달</t>
-  </si>
-  <si>
-    <t>막 아 루인</t>
-  </si>
-  <si>
-    <t>리딜</t>
-  </si>
-  <si>
-    <t>나무 장화</t>
-  </si>
-  <si>
-    <t>강화 나무 장화</t>
-  </si>
-  <si>
-    <t>가죽 장화</t>
-  </si>
-  <si>
-    <t>강화 가죽 장화</t>
-  </si>
-  <si>
-    <t>황동 장화</t>
-  </si>
-  <si>
-    <t>강화 황동 장화</t>
-  </si>
-  <si>
-    <t>철 장화</t>
-  </si>
-  <si>
-    <t>강화 철 장화</t>
-  </si>
-  <si>
-    <t>낡은 옷</t>
-  </si>
-  <si>
-    <t>천 옷</t>
-  </si>
-  <si>
-    <t>강화 천 옷</t>
-  </si>
-  <si>
-    <t>레어 천 옷</t>
-  </si>
-  <si>
-    <t>가죽 옷</t>
-  </si>
-  <si>
-    <t>강화 가죽 옷</t>
-  </si>
-  <si>
-    <t>레어 가죽 옷</t>
-  </si>
-  <si>
-    <t>법사 옷</t>
-  </si>
-  <si>
-    <t>장식된 법사 옷</t>
-  </si>
-  <si>
-    <t>레어 법사 옷</t>
-  </si>
-  <si>
-    <t>가죽 갑옷</t>
-  </si>
-  <si>
-    <t>강화 가죽 갑옷</t>
-  </si>
-  <si>
-    <t>레어 가죽 갑옷</t>
-  </si>
-  <si>
-    <t>미션 보상 무기 상자 01</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>item_box_02</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>drop_0023</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>drop_0024</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>미션 보상 갑옷 상자 01</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>item_box_03</t>
-  </si>
-  <si>
-    <t>미션 보상 갑옷 상자 02</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>item_box_04</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>drop_0025</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>item_equip_n_ar_01</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>item_equip_n_ac_01</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>item_equip_n_bo_01</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ADD_ITEM</t>
-  </si>
-  <si>
-    <t>ADD_ITEM</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>금열쇠</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>item_key_03</t>
-  </si>
-  <si>
-    <t>잠겨있는 구리 상자</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>잠겨있는 은 상자</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>잠겨있는 금 상자</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>item_box_05</t>
-  </si>
-  <si>
-    <t>item_box_06</t>
-  </si>
-  <si>
-    <t>item_box_07</t>
-  </si>
-  <si>
-    <t>item_key_01</t>
-  </si>
-  <si>
-    <t>탄환</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Bullet</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>발사체 이름</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Bullet</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>pf_fire_02</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>pf_blade_01</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>pf_dagger_02</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>pf_blade_04</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>pf_fire_01</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>pf_dagger_01</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>pf_blade_05</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>pf_blade_02</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>pf_ice_01</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>pf_dagger_03</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>pf_water_03</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>pf_water_01</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>출석 보상 A등급 캐릭터 상자 01</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>item_box_08</t>
-  </si>
-  <si>
-    <t>item_summon_01</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>SUMMON</t>
-  </si>
-  <si>
-    <t>icon_item_9002</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>패트릭 소환권</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>drop_0026</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>item_summon_02</t>
-  </si>
-  <si>
-    <t>item_summon_03</t>
-  </si>
-  <si>
-    <t>item_summon_04</t>
-  </si>
-  <si>
-    <t>item_summon_05</t>
-  </si>
-  <si>
-    <t>앤드류 소환권</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>바르반 바르반</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>헤르미나 소환권</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>카네키 소환권</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>조르의 반지</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>item_equip_r_ac_01</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>item_equip_r_ac_02</t>
-  </si>
-  <si>
-    <t>item_equip_r_ac_03</t>
-  </si>
-  <si>
-    <t>item_equip_r_ac_04</t>
-  </si>
-  <si>
-    <t>item_equip_r_ac_05</t>
-  </si>
-  <si>
-    <t>조르의 보석함</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>item_box_09</t>
-  </si>
-  <si>
-    <t>drop_0027</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>좀비의 영혼</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>item_quest_02</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>리비히의 서</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>item_quest_03</t>
-  </si>
-  <si>
-    <t>icon_item_5005</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>icon_item_5006</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>icon_item_3004</t>
-  </si>
-  <si>
-    <t>icon_item_3005</t>
-  </si>
-  <si>
-    <t>icon_item_3006</t>
-  </si>
-  <si>
-    <t>icon_item_3007</t>
-  </si>
-  <si>
-    <t>icon_item_3008</t>
-  </si>
-  <si>
-    <t>icon_item_3009</t>
-  </si>
-  <si>
-    <t>icon_item_3010</t>
-  </si>
-  <si>
-    <t>icon_item_3011</t>
-  </si>
-  <si>
-    <t>icon_item_3012</t>
-  </si>
-  <si>
-    <t>icon_item_2009</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>icon_item_2003</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>icon_item_2008</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>icon_item_2004</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>icon_item_2007</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>icon_item_2006</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>icon_item_2018</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>icon_item_4004</t>
+  </si>
+  <si>
+    <t>icon_item_4005</t>
+  </si>
+  <si>
+    <t>icon_item_4006</t>
+  </si>
+  <si>
+    <t>icon_item_4007</t>
+  </si>
+  <si>
+    <t>icon_item_4008</t>
+  </si>
+  <si>
+    <t>icon_item_4009</t>
+  </si>
+  <si>
+    <t>icon_item_4010</t>
+  </si>
+  <si>
+    <t>icon_item_4011</t>
+  </si>
+  <si>
+    <t>icon_item_4012</t>
+  </si>
+  <si>
+    <t>혼돈 지팡이</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>icon_item_4204</t>
+  </si>
+  <si>
+    <t>icon_item_4205</t>
+  </si>
+  <si>
+    <t>icon_item_4206</t>
+  </si>
+  <si>
+    <t>icon_item_4207</t>
+  </si>
+  <si>
+    <t>icon_item_4208</t>
+  </si>
+  <si>
+    <t>icon_item_4209</t>
+  </si>
+  <si>
+    <t>icon_item_4210</t>
+  </si>
+  <si>
+    <t>icon_item_4211</t>
+  </si>
+  <si>
+    <t>icon_item_4212</t>
+  </si>
+  <si>
+    <t>icon_item_4404</t>
+  </si>
+  <si>
+    <t>icon_item_4405</t>
+  </si>
+  <si>
+    <t>icon_item_4406</t>
+  </si>
+  <si>
+    <t>icon_item_4407</t>
+  </si>
+  <si>
+    <t>icon_item_4408</t>
+  </si>
+  <si>
+    <t>icon_item_4409</t>
+  </si>
+  <si>
+    <t>icon_item_4410</t>
+  </si>
+  <si>
+    <t>icon_item_4411</t>
+  </si>
+  <si>
+    <t>icon_item_4412</t>
+  </si>
+  <si>
+    <t>icon_item_5003</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>파머의 돈주머니</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>item_quest_04</t>
+  </si>
+  <si>
+    <t>icon_item_5007</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>호박</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>item_quest_05</t>
+  </si>
+  <si>
+    <t>item_quest_06</t>
+  </si>
+  <si>
+    <t>이가 빠진 낫</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -4774,10 +4903,10 @@
         <v>15</v>
       </c>
       <c r="B16" s="25" t="s">
-        <v>419</v>
+        <v>412</v>
       </c>
       <c r="C16" s="25" t="s">
-        <v>420</v>
+        <v>413</v>
       </c>
       <c r="D16" s="20" t="s">
         <v>14</v>
@@ -4792,7 +4921,7 @@
         <v>32</v>
       </c>
       <c r="H16" s="26" t="s">
-        <v>421</v>
+        <v>414</v>
       </c>
       <c r="I16" s="1"/>
       <c r="J16" s="1"/>
@@ -5915,7 +6044,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet3"/>
-  <dimension ref="A1:AE122"/>
+  <dimension ref="A1:AE125"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="6.5" style="37" bestFit="1" customWidth="1"/>
@@ -5980,7 +6109,7 @@
         <v>155</v>
       </c>
       <c r="O1" s="32" t="s">
-        <v>422</v>
+        <v>415</v>
       </c>
       <c r="P1" s="31" t="s">
         <v>91</v>
@@ -6476,10 +6605,10 @@
         <v>31000</v>
       </c>
       <c r="B7" s="40" t="s">
-        <v>383</v>
+        <v>376</v>
       </c>
       <c r="C7" s="41" t="s">
-        <v>405</v>
+        <v>398</v>
       </c>
       <c r="D7" s="39" t="str">
         <f t="shared" si="0"/>
@@ -6567,7 +6696,7 @@
         <v>31001</v>
       </c>
       <c r="B8" s="40" t="s">
-        <v>393</v>
+        <v>386</v>
       </c>
       <c r="C8" s="41" t="s">
         <v>177</v>
@@ -6658,7 +6787,7 @@
         <v>31002</v>
       </c>
       <c r="B9" s="40" t="s">
-        <v>394</v>
+        <v>387</v>
       </c>
       <c r="C9" s="41" t="s">
         <v>178</v>
@@ -6749,7 +6878,7 @@
         <v>31003</v>
       </c>
       <c r="B10" s="40" t="s">
-        <v>395</v>
+        <v>388</v>
       </c>
       <c r="C10" s="41" t="s">
         <v>179</v>
@@ -7675,7 +7804,7 @@
         <v>31300</v>
       </c>
       <c r="B20" s="40" t="s">
-        <v>384</v>
+        <v>377</v>
       </c>
       <c r="C20" s="41" t="s">
         <v>180</v>
@@ -7766,7 +7895,7 @@
         <v>31301</v>
       </c>
       <c r="B21" s="40" t="s">
-        <v>385</v>
+        <v>378</v>
       </c>
       <c r="C21" s="41" t="s">
         <v>181</v>
@@ -7857,7 +7986,7 @@
         <v>31302</v>
       </c>
       <c r="B22" s="40" t="s">
-        <v>386</v>
+        <v>379</v>
       </c>
       <c r="C22" s="41" t="s">
         <v>182</v>
@@ -7952,7 +8081,7 @@
         <v>31303</v>
       </c>
       <c r="B23" s="40" t="s">
-        <v>387</v>
+        <v>380</v>
       </c>
       <c r="C23" s="41" t="s">
         <v>201</v>
@@ -8043,7 +8172,7 @@
         <v>31304</v>
       </c>
       <c r="B24" s="40" t="s">
-        <v>388</v>
+        <v>381</v>
       </c>
       <c r="C24" s="41" t="s">
         <v>202</v>
@@ -8134,7 +8263,7 @@
         <v>31305</v>
       </c>
       <c r="B25" s="40" t="s">
-        <v>389</v>
+        <v>382</v>
       </c>
       <c r="C25" s="41" t="s">
         <v>203</v>
@@ -8506,7 +8635,7 @@
         <v>31309</v>
       </c>
       <c r="B29" s="40" t="s">
-        <v>390</v>
+        <v>383</v>
       </c>
       <c r="C29" s="41" t="s">
         <v>213</v>
@@ -8597,7 +8726,7 @@
         <v>31310</v>
       </c>
       <c r="B30" s="40" t="s">
-        <v>391</v>
+        <v>384</v>
       </c>
       <c r="C30" s="41" t="s">
         <v>214</v>
@@ -8688,7 +8817,7 @@
         <v>31311</v>
       </c>
       <c r="B31" s="40" t="s">
-        <v>392</v>
+        <v>385</v>
       </c>
       <c r="C31" s="41" t="s">
         <v>215</v>
@@ -8786,7 +8915,7 @@
         <v>321</v>
       </c>
       <c r="C32" s="36" t="s">
-        <v>406</v>
+        <v>399</v>
       </c>
       <c r="D32" s="34" t="str">
         <f t="shared" si="0"/>
@@ -9124,7 +9253,7 @@
         <v>0</v>
       </c>
       <c r="AB35" s="37" t="s">
-        <v>287</v>
+        <v>473</v>
       </c>
       <c r="AC35" s="37" t="s">
         <v>41</v>
@@ -9317,7 +9446,7 @@
         <v>32006</v>
       </c>
       <c r="B38" s="35" t="s">
-        <v>327</v>
+        <v>468</v>
       </c>
       <c r="C38" s="36" t="s">
         <v>216</v>
@@ -9394,7 +9523,7 @@
         <v>0</v>
       </c>
       <c r="AB38" s="37" t="s">
-        <v>287</v>
+        <v>474</v>
       </c>
       <c r="AC38" s="37" t="s">
         <v>41</v>
@@ -9411,7 +9540,7 @@
         <v>32007</v>
       </c>
       <c r="B39" s="35" t="s">
-        <v>328</v>
+        <v>470</v>
       </c>
       <c r="C39" s="36" t="s">
         <v>217</v>
@@ -9482,7 +9611,7 @@
         <v>0</v>
       </c>
       <c r="AB39" s="37" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="AC39" s="37" t="s">
         <v>41</v>
@@ -9499,7 +9628,7 @@
         <v>32008</v>
       </c>
       <c r="B40" s="35" t="s">
-        <v>329</v>
+        <v>478</v>
       </c>
       <c r="C40" s="36" t="s">
         <v>218</v>
@@ -9570,7 +9699,7 @@
         <v>0</v>
       </c>
       <c r="AB40" s="37" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="AC40" s="37" t="s">
         <v>41</v>
@@ -9587,7 +9716,7 @@
         <v>32009</v>
       </c>
       <c r="B41" s="35" t="s">
-        <v>330</v>
+        <v>469</v>
       </c>
       <c r="C41" s="36" t="s">
         <v>219</v>
@@ -9664,7 +9793,7 @@
         <v>0</v>
       </c>
       <c r="AB41" s="37" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="AC41" s="37" t="s">
         <v>41</v>
@@ -9681,7 +9810,7 @@
         <v>32010</v>
       </c>
       <c r="B42" s="35" t="s">
-        <v>331</v>
+        <v>471</v>
       </c>
       <c r="C42" s="36" t="s">
         <v>220</v>
@@ -9752,7 +9881,7 @@
         <v>0</v>
       </c>
       <c r="AB42" s="37" t="s">
-        <v>476</v>
+        <v>479</v>
       </c>
       <c r="AC42" s="37" t="s">
         <v>41</v>
@@ -9769,7 +9898,7 @@
         <v>32011</v>
       </c>
       <c r="B43" s="35" t="s">
-        <v>332</v>
+        <v>327</v>
       </c>
       <c r="C43" s="36" t="s">
         <v>221</v>
@@ -9840,7 +9969,7 @@
         <v>0</v>
       </c>
       <c r="AB43" s="37" t="s">
-        <v>478</v>
+        <v>467</v>
       </c>
       <c r="AC43" s="37" t="s">
         <v>41</v>
@@ -9857,7 +9986,7 @@
         <v>32012</v>
       </c>
       <c r="B44" s="35" t="s">
-        <v>333</v>
+        <v>472</v>
       </c>
       <c r="C44" s="36" t="s">
         <v>222</v>
@@ -9934,7 +10063,7 @@
         <v>0</v>
       </c>
       <c r="AB44" s="37" t="s">
-        <v>474</v>
+        <v>480</v>
       </c>
       <c r="AC44" s="37" t="s">
         <v>41</v>
@@ -9951,10 +10080,10 @@
         <v>32013</v>
       </c>
       <c r="B45" s="35" t="s">
-        <v>450</v>
+        <v>443</v>
       </c>
       <c r="C45" s="36" t="s">
-        <v>451</v>
+        <v>444</v>
       </c>
       <c r="D45" s="34" t="str">
         <f t="shared" si="24"/>
@@ -10045,10 +10174,10 @@
         <v>32014</v>
       </c>
       <c r="B46" s="35" t="s">
-        <v>450</v>
+        <v>443</v>
       </c>
       <c r="C46" s="36" t="s">
-        <v>452</v>
+        <v>445</v>
       </c>
       <c r="D46" s="34" t="str">
         <f t="shared" ref="D46" si="26">"STR_"&amp;UPPER(C46)</f>
@@ -10139,10 +10268,10 @@
         <v>32015</v>
       </c>
       <c r="B47" s="35" t="s">
-        <v>450</v>
+        <v>443</v>
       </c>
       <c r="C47" s="36" t="s">
-        <v>453</v>
+        <v>446</v>
       </c>
       <c r="D47" s="34" t="str">
         <f t="shared" ref="D47" si="28">"STR_"&amp;UPPER(C47)</f>
@@ -10233,10 +10362,10 @@
         <v>32016</v>
       </c>
       <c r="B48" s="35" t="s">
-        <v>450</v>
+        <v>443</v>
       </c>
       <c r="C48" s="36" t="s">
-        <v>454</v>
+        <v>447</v>
       </c>
       <c r="D48" s="34" t="str">
         <f t="shared" si="24"/>
@@ -10327,10 +10456,10 @@
         <v>32017</v>
       </c>
       <c r="B49" s="35" t="s">
-        <v>450</v>
+        <v>443</v>
       </c>
       <c r="C49" s="36" t="s">
-        <v>455</v>
+        <v>448</v>
       </c>
       <c r="D49" s="34" t="str">
         <f t="shared" ref="D49" si="30">"STR_"&amp;UPPER(C49)</f>
@@ -10421,10 +10550,10 @@
         <v>33000</v>
       </c>
       <c r="B50" s="40" t="s">
-        <v>334</v>
+        <v>328</v>
       </c>
       <c r="C50" s="41" t="s">
-        <v>407</v>
+        <v>400</v>
       </c>
       <c r="D50" s="39" t="str">
         <f t="shared" si="0"/>
@@ -10512,7 +10641,7 @@
         <v>33001</v>
       </c>
       <c r="B51" s="40" t="s">
-        <v>336</v>
+        <v>330</v>
       </c>
       <c r="C51" s="41" t="s">
         <v>188</v>
@@ -10603,7 +10732,7 @@
         <v>33002</v>
       </c>
       <c r="B52" s="40" t="s">
-        <v>375</v>
+        <v>368</v>
       </c>
       <c r="C52" s="41" t="s">
         <v>189</v>
@@ -10694,7 +10823,7 @@
         <v>33003</v>
       </c>
       <c r="B53" s="40" t="s">
-        <v>376</v>
+        <v>369</v>
       </c>
       <c r="C53" s="41" t="s">
         <v>190</v>
@@ -10789,7 +10918,7 @@
         <v>33004</v>
       </c>
       <c r="B54" s="40" t="s">
-        <v>335</v>
+        <v>329</v>
       </c>
       <c r="C54" s="41" t="s">
         <v>229</v>
@@ -10863,7 +10992,7 @@
         <v>0</v>
       </c>
       <c r="AB54" s="39" t="s">
-        <v>465</v>
+        <v>458</v>
       </c>
       <c r="AC54" s="39" t="s">
         <v>41</v>
@@ -10880,7 +11009,7 @@
         <v>33005</v>
       </c>
       <c r="B55" s="40" t="s">
-        <v>377</v>
+        <v>370</v>
       </c>
       <c r="C55" s="41" t="s">
         <v>223</v>
@@ -10954,7 +11083,7 @@
         <v>0</v>
       </c>
       <c r="AB55" s="39" t="s">
-        <v>466</v>
+        <v>459</v>
       </c>
       <c r="AC55" s="39" t="s">
         <v>41</v>
@@ -10971,7 +11100,7 @@
         <v>33006</v>
       </c>
       <c r="B56" s="40" t="s">
-        <v>378</v>
+        <v>371</v>
       </c>
       <c r="C56" s="41" t="s">
         <v>224</v>
@@ -11049,7 +11178,7 @@
         <v>0</v>
       </c>
       <c r="AB56" s="39" t="s">
-        <v>467</v>
+        <v>460</v>
       </c>
       <c r="AC56" s="39" t="s">
         <v>41</v>
@@ -11066,7 +11195,7 @@
         <v>33007</v>
       </c>
       <c r="B57" s="40" t="s">
-        <v>337</v>
+        <v>331</v>
       </c>
       <c r="C57" s="41" t="s">
         <v>230</v>
@@ -11134,7 +11263,7 @@
         <v>0</v>
       </c>
       <c r="AB57" s="39" t="s">
-        <v>468</v>
+        <v>461</v>
       </c>
       <c r="AC57" s="39" t="s">
         <v>41</v>
@@ -11151,7 +11280,7 @@
         <v>33008</v>
       </c>
       <c r="B58" s="40" t="s">
-        <v>379</v>
+        <v>372</v>
       </c>
       <c r="C58" s="41" t="s">
         <v>225</v>
@@ -11225,7 +11354,7 @@
         <v>0</v>
       </c>
       <c r="AB58" s="39" t="s">
-        <v>469</v>
+        <v>462</v>
       </c>
       <c r="AC58" s="39" t="s">
         <v>41</v>
@@ -11242,7 +11371,7 @@
         <v>33009</v>
       </c>
       <c r="B59" s="40" t="s">
-        <v>380</v>
+        <v>373</v>
       </c>
       <c r="C59" s="41" t="s">
         <v>226</v>
@@ -11320,7 +11449,7 @@
         <v>0</v>
       </c>
       <c r="AB59" s="39" t="s">
-        <v>470</v>
+        <v>463</v>
       </c>
       <c r="AC59" s="39" t="s">
         <v>41</v>
@@ -11337,7 +11466,7 @@
         <v>33010</v>
       </c>
       <c r="B60" s="40" t="s">
-        <v>338</v>
+        <v>332</v>
       </c>
       <c r="C60" s="41" t="s">
         <v>231</v>
@@ -11411,7 +11540,7 @@
         <v>0</v>
       </c>
       <c r="AB60" s="39" t="s">
-        <v>471</v>
+        <v>464</v>
       </c>
       <c r="AC60" s="39" t="s">
         <v>41</v>
@@ -11428,7 +11557,7 @@
         <v>33011</v>
       </c>
       <c r="B61" s="40" t="s">
-        <v>381</v>
+        <v>374</v>
       </c>
       <c r="C61" s="41" t="s">
         <v>227</v>
@@ -11496,7 +11625,7 @@
         <v>0</v>
       </c>
       <c r="AB61" s="39" t="s">
-        <v>472</v>
+        <v>465</v>
       </c>
       <c r="AC61" s="39" t="s">
         <v>41</v>
@@ -11513,7 +11642,7 @@
         <v>33012</v>
       </c>
       <c r="B62" s="40" t="s">
-        <v>382</v>
+        <v>375</v>
       </c>
       <c r="C62" s="41" t="s">
         <v>228</v>
@@ -11591,7 +11720,7 @@
         <v>0</v>
       </c>
       <c r="AB62" s="39" t="s">
-        <v>473</v>
+        <v>466</v>
       </c>
       <c r="AC62" s="39" t="s">
         <v>41</v>
@@ -11608,7 +11737,7 @@
         <v>34000</v>
       </c>
       <c r="B63" s="35" t="s">
-        <v>339</v>
+        <v>333</v>
       </c>
       <c r="C63" s="36" t="s">
         <v>232</v>
@@ -11649,7 +11778,7 @@
         <v>0</v>
       </c>
       <c r="O63" s="37" t="s">
-        <v>424</v>
+        <v>417</v>
       </c>
       <c r="P63" s="34" t="s">
         <v>44</v>
@@ -11690,7 +11819,7 @@
         <v>34001</v>
       </c>
       <c r="B64" s="35" t="s">
-        <v>352</v>
+        <v>345</v>
       </c>
       <c r="C64" s="36" t="s">
         <v>191</v>
@@ -11731,7 +11860,7 @@
         <v>0</v>
       </c>
       <c r="O64" s="37" t="s">
-        <v>424</v>
+        <v>417</v>
       </c>
       <c r="P64" s="34" t="s">
         <v>44</v>
@@ -11772,7 +11901,7 @@
         <v>34002</v>
       </c>
       <c r="B65" s="35" t="s">
-        <v>340</v>
+        <v>334</v>
       </c>
       <c r="C65" s="36" t="s">
         <v>192</v>
@@ -11813,7 +11942,7 @@
         <v>0</v>
       </c>
       <c r="O65" s="37" t="s">
-        <v>424</v>
+        <v>417</v>
       </c>
       <c r="P65" s="34" t="s">
         <v>44</v>
@@ -11854,7 +11983,7 @@
         <v>34003</v>
       </c>
       <c r="B66" s="35" t="s">
-        <v>371</v>
+        <v>364</v>
       </c>
       <c r="C66" s="36" t="s">
         <v>193</v>
@@ -11895,7 +12024,7 @@
         <v>0</v>
       </c>
       <c r="O66" s="37" t="s">
-        <v>424</v>
+        <v>417</v>
       </c>
       <c r="P66" s="34" t="s">
         <v>44</v>
@@ -11951,7 +12080,7 @@
         <v>34010</v>
       </c>
       <c r="B67" s="35" t="s">
-        <v>353</v>
+        <v>346</v>
       </c>
       <c r="C67" s="36" t="s">
         <v>260</v>
@@ -11992,7 +12121,7 @@
         <v>0</v>
       </c>
       <c r="O67" s="37" t="s">
-        <v>424</v>
+        <v>417</v>
       </c>
       <c r="P67" s="34" t="s">
         <v>44</v>
@@ -12016,7 +12145,7 @@
         <v>0</v>
       </c>
       <c r="AB67" s="37" t="s">
-        <v>291</v>
+        <v>481</v>
       </c>
       <c r="AC67" s="37" t="s">
         <v>41</v>
@@ -12033,7 +12162,7 @@
         <v>34011</v>
       </c>
       <c r="B68" s="35" t="s">
-        <v>354</v>
+        <v>347</v>
       </c>
       <c r="C68" s="36" t="s">
         <v>236</v>
@@ -12074,7 +12203,7 @@
         <v>0</v>
       </c>
       <c r="O68" s="37" t="s">
-        <v>426</v>
+        <v>419</v>
       </c>
       <c r="P68" s="34" t="s">
         <v>44</v>
@@ -12098,7 +12227,7 @@
         <v>0</v>
       </c>
       <c r="AB68" s="37" t="s">
-        <v>292</v>
+        <v>482</v>
       </c>
       <c r="AC68" s="37" t="s">
         <v>41</v>
@@ -12115,7 +12244,7 @@
         <v>34012</v>
       </c>
       <c r="B69" s="35" t="s">
-        <v>370</v>
+        <v>363</v>
       </c>
       <c r="C69" s="36" t="s">
         <v>237</v>
@@ -12156,7 +12285,7 @@
         <v>0</v>
       </c>
       <c r="O69" s="37" t="s">
-        <v>426</v>
+        <v>419</v>
       </c>
       <c r="P69" s="34" t="s">
         <v>44</v>
@@ -12195,7 +12324,7 @@
         <v>0</v>
       </c>
       <c r="AB69" s="37" t="s">
-        <v>293</v>
+        <v>483</v>
       </c>
       <c r="AC69" s="37" t="s">
         <v>41</v>
@@ -12212,7 +12341,7 @@
         <v>34019</v>
       </c>
       <c r="B70" s="35" t="s">
-        <v>356</v>
+        <v>349</v>
       </c>
       <c r="C70" s="36" t="s">
         <v>261</v>
@@ -12253,7 +12382,7 @@
         <v>0</v>
       </c>
       <c r="O70" s="37" t="s">
-        <v>424</v>
+        <v>417</v>
       </c>
       <c r="P70" s="34" t="s">
         <v>44</v>
@@ -12277,7 +12406,7 @@
         <v>0</v>
       </c>
       <c r="AB70" s="37" t="s">
-        <v>291</v>
+        <v>484</v>
       </c>
       <c r="AC70" s="37" t="s">
         <v>41</v>
@@ -12294,7 +12423,7 @@
         <v>34020</v>
       </c>
       <c r="B71" s="35" t="s">
-        <v>355</v>
+        <v>348</v>
       </c>
       <c r="C71" s="36" t="s">
         <v>244</v>
@@ -12335,7 +12464,7 @@
         <v>0</v>
       </c>
       <c r="O71" s="37" t="s">
-        <v>429</v>
+        <v>422</v>
       </c>
       <c r="P71" s="34" t="s">
         <v>44</v>
@@ -12359,7 +12488,7 @@
         <v>0</v>
       </c>
       <c r="AB71" s="37" t="s">
-        <v>292</v>
+        <v>485</v>
       </c>
       <c r="AC71" s="37" t="s">
         <v>41</v>
@@ -12376,7 +12505,7 @@
         <v>34021</v>
       </c>
       <c r="B72" s="35" t="s">
-        <v>372</v>
+        <v>365</v>
       </c>
       <c r="C72" s="36" t="s">
         <v>245</v>
@@ -12417,7 +12546,7 @@
         <v>0</v>
       </c>
       <c r="O72" s="37" t="s">
-        <v>429</v>
+        <v>422</v>
       </c>
       <c r="P72" s="34" t="s">
         <v>44</v>
@@ -12456,7 +12585,7 @@
         <v>0</v>
       </c>
       <c r="AB72" s="37" t="s">
-        <v>293</v>
+        <v>486</v>
       </c>
       <c r="AC72" s="37" t="s">
         <v>41</v>
@@ -12473,7 +12602,7 @@
         <v>34028</v>
       </c>
       <c r="B73" s="35" t="s">
-        <v>357</v>
+        <v>350</v>
       </c>
       <c r="C73" s="36" t="s">
         <v>262</v>
@@ -12514,7 +12643,7 @@
         <v>0</v>
       </c>
       <c r="O73" s="37" t="s">
-        <v>424</v>
+        <v>417</v>
       </c>
       <c r="P73" s="34" t="s">
         <v>44</v>
@@ -12538,7 +12667,7 @@
         <v>0</v>
       </c>
       <c r="AB73" s="37" t="s">
-        <v>291</v>
+        <v>487</v>
       </c>
       <c r="AC73" s="37" t="s">
         <v>41</v>
@@ -12555,7 +12684,7 @@
         <v>34029</v>
       </c>
       <c r="B74" s="35" t="s">
-        <v>358</v>
+        <v>351</v>
       </c>
       <c r="C74" s="36" t="s">
         <v>252</v>
@@ -12596,7 +12725,7 @@
         <v>0</v>
       </c>
       <c r="O74" s="37" t="s">
-        <v>429</v>
+        <v>422</v>
       </c>
       <c r="P74" s="34" t="s">
         <v>44</v>
@@ -12620,7 +12749,7 @@
         <v>0</v>
       </c>
       <c r="AB74" s="37" t="s">
-        <v>292</v>
+        <v>488</v>
       </c>
       <c r="AC74" s="37" t="s">
         <v>41</v>
@@ -12637,7 +12766,7 @@
         <v>34030</v>
       </c>
       <c r="B75" s="35" t="s">
-        <v>373</v>
+        <v>366</v>
       </c>
       <c r="C75" s="36" t="s">
         <v>253</v>
@@ -12678,7 +12807,7 @@
         <v>0</v>
       </c>
       <c r="O75" s="37" t="s">
-        <v>430</v>
+        <v>423</v>
       </c>
       <c r="P75" s="34" t="s">
         <v>44</v>
@@ -12717,7 +12846,7 @@
         <v>0</v>
       </c>
       <c r="AB75" s="37" t="s">
-        <v>293</v>
+        <v>489</v>
       </c>
       <c r="AC75" s="37" t="s">
         <v>41</v>
@@ -12775,7 +12904,7 @@
         <v>0</v>
       </c>
       <c r="O76" s="37" t="s">
-        <v>423</v>
+        <v>416</v>
       </c>
       <c r="P76" s="34" t="s">
         <v>44</v>
@@ -12816,7 +12945,7 @@
         <v>34201</v>
       </c>
       <c r="B77" s="35" t="s">
-        <v>341</v>
+        <v>335</v>
       </c>
       <c r="C77" s="36" t="s">
         <v>195</v>
@@ -12857,7 +12986,7 @@
         <v>0</v>
       </c>
       <c r="O77" s="37" t="s">
-        <v>423</v>
+        <v>416</v>
       </c>
       <c r="P77" s="34" t="s">
         <v>44</v>
@@ -12898,7 +13027,7 @@
         <v>34202</v>
       </c>
       <c r="B78" s="35" t="s">
-        <v>342</v>
+        <v>336</v>
       </c>
       <c r="C78" s="36" t="s">
         <v>196</v>
@@ -12939,7 +13068,7 @@
         <v>0</v>
       </c>
       <c r="O78" s="37" t="s">
-        <v>423</v>
+        <v>416</v>
       </c>
       <c r="P78" s="34" t="s">
         <v>44</v>
@@ -12995,7 +13124,7 @@
         <v>34203</v>
       </c>
       <c r="B79" s="35" t="s">
-        <v>345</v>
+        <v>339</v>
       </c>
       <c r="C79" s="36" t="s">
         <v>238</v>
@@ -13036,7 +13165,7 @@
         <v>0</v>
       </c>
       <c r="O79" s="37" t="s">
-        <v>423</v>
+        <v>416</v>
       </c>
       <c r="P79" s="34" t="s">
         <v>44</v>
@@ -13060,7 +13189,7 @@
         <v>0</v>
       </c>
       <c r="AB79" s="37" t="s">
-        <v>294</v>
+        <v>491</v>
       </c>
       <c r="AC79" s="37" t="s">
         <v>41</v>
@@ -13077,7 +13206,7 @@
         <v>34204</v>
       </c>
       <c r="B80" s="35" t="s">
-        <v>346</v>
+        <v>340</v>
       </c>
       <c r="C80" s="36" t="s">
         <v>239</v>
@@ -13118,7 +13247,7 @@
         <v>0</v>
       </c>
       <c r="O80" s="37" t="s">
-        <v>423</v>
+        <v>416</v>
       </c>
       <c r="P80" s="34" t="s">
         <v>44</v>
@@ -13142,7 +13271,7 @@
         <v>0</v>
       </c>
       <c r="AB80" s="37" t="s">
-        <v>295</v>
+        <v>492</v>
       </c>
       <c r="AC80" s="37" t="s">
         <v>41</v>
@@ -13159,7 +13288,7 @@
         <v>34205</v>
       </c>
       <c r="B81" s="35" t="s">
-        <v>343</v>
+        <v>337</v>
       </c>
       <c r="C81" s="36" t="s">
         <v>240</v>
@@ -13200,7 +13329,7 @@
         <v>0</v>
       </c>
       <c r="O81" s="37" t="s">
-        <v>427</v>
+        <v>420</v>
       </c>
       <c r="P81" s="34" t="s">
         <v>44</v>
@@ -13239,7 +13368,7 @@
         <v>0</v>
       </c>
       <c r="AB81" s="37" t="s">
-        <v>296</v>
+        <v>493</v>
       </c>
       <c r="AC81" s="37" t="s">
         <v>41</v>
@@ -13256,7 +13385,7 @@
         <v>34206</v>
       </c>
       <c r="B82" s="35" t="s">
-        <v>347</v>
+        <v>341</v>
       </c>
       <c r="C82" s="36" t="s">
         <v>246</v>
@@ -13297,7 +13426,7 @@
         <v>0</v>
       </c>
       <c r="O82" s="37" t="s">
-        <v>434</v>
+        <v>427</v>
       </c>
       <c r="P82" s="34" t="s">
         <v>44</v>
@@ -13321,7 +13450,7 @@
         <v>0</v>
       </c>
       <c r="AB82" s="37" t="s">
-        <v>294</v>
+        <v>494</v>
       </c>
       <c r="AC82" s="37" t="s">
         <v>41</v>
@@ -13338,7 +13467,7 @@
         <v>34207</v>
       </c>
       <c r="B83" s="35" t="s">
-        <v>348</v>
+        <v>490</v>
       </c>
       <c r="C83" s="36" t="s">
         <v>247</v>
@@ -13379,7 +13508,7 @@
         <v>0</v>
       </c>
       <c r="O83" s="37" t="s">
-        <v>434</v>
+        <v>427</v>
       </c>
       <c r="P83" s="34" t="s">
         <v>44</v>
@@ -13403,7 +13532,7 @@
         <v>0</v>
       </c>
       <c r="AB83" s="37" t="s">
-        <v>295</v>
+        <v>495</v>
       </c>
       <c r="AC83" s="37" t="s">
         <v>41</v>
@@ -13420,7 +13549,7 @@
         <v>34208</v>
       </c>
       <c r="B84" s="35" t="s">
-        <v>344</v>
+        <v>338</v>
       </c>
       <c r="C84" s="36" t="s">
         <v>248</v>
@@ -13461,7 +13590,7 @@
         <v>0</v>
       </c>
       <c r="O84" s="37" t="s">
-        <v>427</v>
+        <v>420</v>
       </c>
       <c r="P84" s="34" t="s">
         <v>44</v>
@@ -13500,7 +13629,7 @@
         <v>0</v>
       </c>
       <c r="AB84" s="37" t="s">
-        <v>296</v>
+        <v>496</v>
       </c>
       <c r="AC84" s="37" t="s">
         <v>41</v>
@@ -13517,7 +13646,7 @@
         <v>34209</v>
       </c>
       <c r="B85" s="35" t="s">
-        <v>349</v>
+        <v>342</v>
       </c>
       <c r="C85" s="36" t="s">
         <v>254</v>
@@ -13558,7 +13687,7 @@
         <v>0</v>
       </c>
       <c r="O85" s="37" t="s">
-        <v>433</v>
+        <v>426</v>
       </c>
       <c r="P85" s="34" t="s">
         <v>44</v>
@@ -13582,7 +13711,7 @@
         <v>0</v>
       </c>
       <c r="AB85" s="37" t="s">
-        <v>294</v>
+        <v>497</v>
       </c>
       <c r="AC85" s="37" t="s">
         <v>41</v>
@@ -13599,7 +13728,7 @@
         <v>34210</v>
       </c>
       <c r="B86" s="35" t="s">
-        <v>350</v>
+        <v>343</v>
       </c>
       <c r="C86" s="36" t="s">
         <v>255</v>
@@ -13640,7 +13769,7 @@
         <v>0</v>
       </c>
       <c r="O86" s="37" t="s">
-        <v>433</v>
+        <v>426</v>
       </c>
       <c r="P86" s="34" t="s">
         <v>44</v>
@@ -13664,7 +13793,7 @@
         <v>0</v>
       </c>
       <c r="AB86" s="37" t="s">
-        <v>295</v>
+        <v>498</v>
       </c>
       <c r="AC86" s="37" t="s">
         <v>41</v>
@@ -13681,7 +13810,7 @@
         <v>34211</v>
       </c>
       <c r="B87" s="35" t="s">
-        <v>351</v>
+        <v>344</v>
       </c>
       <c r="C87" s="36" t="s">
         <v>256</v>
@@ -13722,7 +13851,7 @@
         <v>0</v>
       </c>
       <c r="O87" s="37" t="s">
-        <v>431</v>
+        <v>424</v>
       </c>
       <c r="P87" s="34" t="s">
         <v>44</v>
@@ -13761,7 +13890,7 @@
         <v>0</v>
       </c>
       <c r="AB87" s="37" t="s">
-        <v>296</v>
+        <v>499</v>
       </c>
       <c r="AC87" s="37" t="s">
         <v>41</v>
@@ -13778,7 +13907,7 @@
         <v>34400</v>
       </c>
       <c r="B88" s="35" t="s">
-        <v>359</v>
+        <v>352</v>
       </c>
       <c r="C88" s="36" t="s">
         <v>233</v>
@@ -13819,7 +13948,7 @@
         <v>0</v>
       </c>
       <c r="O88" s="37" t="s">
-        <v>425</v>
+        <v>418</v>
       </c>
       <c r="P88" s="34" t="s">
         <v>44</v>
@@ -13860,7 +13989,7 @@
         <v>34401</v>
       </c>
       <c r="B89" s="35" t="s">
-        <v>360</v>
+        <v>353</v>
       </c>
       <c r="C89" s="36" t="s">
         <v>234</v>
@@ -13901,7 +14030,7 @@
         <v>0</v>
       </c>
       <c r="O89" s="37" t="s">
-        <v>425</v>
+        <v>418</v>
       </c>
       <c r="P89" s="34" t="s">
         <v>44</v>
@@ -13942,7 +14071,7 @@
         <v>34402</v>
       </c>
       <c r="B90" s="35" t="s">
-        <v>365</v>
+        <v>358</v>
       </c>
       <c r="C90" s="36" t="s">
         <v>235</v>
@@ -13983,7 +14112,7 @@
         <v>0</v>
       </c>
       <c r="O90" s="37" t="s">
-        <v>425</v>
+        <v>418</v>
       </c>
       <c r="P90" s="34" t="s">
         <v>44</v>
@@ -14039,7 +14168,7 @@
         <v>34403</v>
       </c>
       <c r="B91" s="35" t="s">
-        <v>361</v>
+        <v>354</v>
       </c>
       <c r="C91" s="36" t="s">
         <v>241</v>
@@ -14080,7 +14209,7 @@
         <v>0</v>
       </c>
       <c r="O91" s="37" t="s">
-        <v>425</v>
+        <v>418</v>
       </c>
       <c r="P91" s="34" t="s">
         <v>44</v>
@@ -14104,7 +14233,7 @@
         <v>0</v>
       </c>
       <c r="AB91" s="37" t="s">
-        <v>297</v>
+        <v>500</v>
       </c>
       <c r="AC91" s="37" t="s">
         <v>41</v>
@@ -14121,7 +14250,7 @@
         <v>34404</v>
       </c>
       <c r="B92" s="35" t="s">
-        <v>362</v>
+        <v>355</v>
       </c>
       <c r="C92" s="36" t="s">
         <v>242</v>
@@ -14162,7 +14291,7 @@
         <v>0</v>
       </c>
       <c r="O92" s="37" t="s">
-        <v>425</v>
+        <v>418</v>
       </c>
       <c r="P92" s="34" t="s">
         <v>44</v>
@@ -14186,7 +14315,7 @@
         <v>0</v>
       </c>
       <c r="AB92" s="37" t="s">
-        <v>298</v>
+        <v>501</v>
       </c>
       <c r="AC92" s="37" t="s">
         <v>41</v>
@@ -14203,7 +14332,7 @@
         <v>34405</v>
       </c>
       <c r="B93" s="35" t="s">
-        <v>366</v>
+        <v>359</v>
       </c>
       <c r="C93" s="36" t="s">
         <v>243</v>
@@ -14244,7 +14373,7 @@
         <v>0</v>
       </c>
       <c r="O93" s="37" t="s">
-        <v>428</v>
+        <v>421</v>
       </c>
       <c r="P93" s="34" t="s">
         <v>44</v>
@@ -14283,7 +14412,7 @@
         <v>0</v>
       </c>
       <c r="AB93" s="37" t="s">
-        <v>299</v>
+        <v>502</v>
       </c>
       <c r="AC93" s="37" t="s">
         <v>41</v>
@@ -14300,7 +14429,7 @@
         <v>34406</v>
       </c>
       <c r="B94" s="35" t="s">
-        <v>363</v>
+        <v>356</v>
       </c>
       <c r="C94" s="36" t="s">
         <v>249</v>
@@ -14341,7 +14470,7 @@
         <v>0</v>
       </c>
       <c r="O94" s="37" t="s">
-        <v>425</v>
+        <v>418</v>
       </c>
       <c r="P94" s="34" t="s">
         <v>44</v>
@@ -14365,7 +14494,7 @@
         <v>0</v>
       </c>
       <c r="AB94" s="37" t="s">
-        <v>297</v>
+        <v>503</v>
       </c>
       <c r="AC94" s="37" t="s">
         <v>41</v>
@@ -14382,7 +14511,7 @@
         <v>34407</v>
       </c>
       <c r="B95" s="35" t="s">
-        <v>364</v>
+        <v>357</v>
       </c>
       <c r="C95" s="36" t="s">
         <v>250</v>
@@ -14423,7 +14552,7 @@
         <v>0</v>
       </c>
       <c r="O95" s="37" t="s">
-        <v>428</v>
+        <v>421</v>
       </c>
       <c r="P95" s="34" t="s">
         <v>44</v>
@@ -14447,7 +14576,7 @@
         <v>0</v>
       </c>
       <c r="AB95" s="37" t="s">
-        <v>298</v>
+        <v>504</v>
       </c>
       <c r="AC95" s="37" t="s">
         <v>41</v>
@@ -14464,7 +14593,7 @@
         <v>34408</v>
       </c>
       <c r="B96" s="35" t="s">
-        <v>374</v>
+        <v>367</v>
       </c>
       <c r="C96" s="36" t="s">
         <v>251</v>
@@ -14505,7 +14634,7 @@
         <v>0</v>
       </c>
       <c r="O96" s="37" t="s">
-        <v>428</v>
+        <v>421</v>
       </c>
       <c r="P96" s="34" t="s">
         <v>44</v>
@@ -14544,7 +14673,7 @@
         <v>0</v>
       </c>
       <c r="AB96" s="37" t="s">
-        <v>299</v>
+        <v>505</v>
       </c>
       <c r="AC96" s="37" t="s">
         <v>41</v>
@@ -14561,7 +14690,7 @@
         <v>34409</v>
       </c>
       <c r="B97" s="35" t="s">
-        <v>369</v>
+        <v>362</v>
       </c>
       <c r="C97" s="36" t="s">
         <v>257</v>
@@ -14602,7 +14731,7 @@
         <v>0</v>
       </c>
       <c r="O97" s="37" t="s">
-        <v>425</v>
+        <v>418</v>
       </c>
       <c r="P97" s="34" t="s">
         <v>44</v>
@@ -14626,7 +14755,7 @@
         <v>0</v>
       </c>
       <c r="AB97" s="37" t="s">
-        <v>297</v>
+        <v>506</v>
       </c>
       <c r="AC97" s="37" t="s">
         <v>41</v>
@@ -14643,7 +14772,7 @@
         <v>34410</v>
       </c>
       <c r="B98" s="35" t="s">
-        <v>367</v>
+        <v>360</v>
       </c>
       <c r="C98" s="36" t="s">
         <v>258</v>
@@ -14684,7 +14813,7 @@
         <v>0</v>
       </c>
       <c r="O98" s="37" t="s">
-        <v>428</v>
+        <v>421</v>
       </c>
       <c r="P98" s="34" t="s">
         <v>44</v>
@@ -14708,7 +14837,7 @@
         <v>0</v>
       </c>
       <c r="AB98" s="37" t="s">
-        <v>298</v>
+        <v>507</v>
       </c>
       <c r="AC98" s="37" t="s">
         <v>41</v>
@@ -14725,7 +14854,7 @@
         <v>34411</v>
       </c>
       <c r="B99" s="35" t="s">
-        <v>368</v>
+        <v>361</v>
       </c>
       <c r="C99" s="36" t="s">
         <v>259</v>
@@ -14766,7 +14895,7 @@
         <v>0</v>
       </c>
       <c r="O99" s="37" t="s">
-        <v>432</v>
+        <v>425</v>
       </c>
       <c r="P99" s="34" t="s">
         <v>44</v>
@@ -14805,7 +14934,7 @@
         <v>0</v>
       </c>
       <c r="AB99" s="37" t="s">
-        <v>299</v>
+        <v>508</v>
       </c>
       <c r="AC99" s="37" t="s">
         <v>41</v>
@@ -14828,11 +14957,11 @@
         <v>111</v>
       </c>
       <c r="D100" s="39" t="str">
-        <f t="shared" ref="D100:D116" si="44">"STR_"&amp;UPPER(C100)</f>
+        <f t="shared" ref="D100:D119" si="44">"STR_"&amp;UPPER(C100)</f>
         <v>STR_ITEM_BOX_01</v>
       </c>
       <c r="E100" s="39" t="str">
-        <f t="shared" ref="E100:E116" si="45">D100&amp;"_DESC"</f>
+        <f t="shared" ref="E100:E119" si="45">D100&amp;"_DESC"</f>
         <v>STR_ITEM_BOX_01_DESC</v>
       </c>
       <c r="F100" s="39">
@@ -14864,7 +14993,7 @@
       </c>
       <c r="O100" s="39"/>
       <c r="P100" s="39" t="s">
-        <v>408</v>
+        <v>401</v>
       </c>
       <c r="Q100" s="39">
         <v>1</v>
@@ -14903,10 +15032,10 @@
         <v>35001</v>
       </c>
       <c r="B101" s="40" t="s">
-        <v>396</v>
+        <v>389</v>
       </c>
       <c r="C101" s="41" t="s">
-        <v>397</v>
+        <v>390</v>
       </c>
       <c r="D101" s="39" t="str">
         <f t="shared" ref="D101:D102" si="46">"STR_"&amp;UPPER(C101)</f>
@@ -14945,7 +15074,7 @@
       </c>
       <c r="O101" s="39"/>
       <c r="P101" s="39" t="s">
-        <v>408</v>
+        <v>401</v>
       </c>
       <c r="Q101" s="39">
         <v>1</v>
@@ -14974,7 +15103,7 @@
         <v>125</v>
       </c>
       <c r="AC101" s="39" t="s">
-        <v>398</v>
+        <v>391</v>
       </c>
       <c r="AD101" s="39"/>
       <c r="AE101" s="39"/>
@@ -14984,10 +15113,10 @@
         <v>35002</v>
       </c>
       <c r="B102" s="40" t="s">
-        <v>400</v>
+        <v>393</v>
       </c>
       <c r="C102" s="41" t="s">
-        <v>401</v>
+        <v>394</v>
       </c>
       <c r="D102" s="39" t="str">
         <f t="shared" si="46"/>
@@ -15026,7 +15155,7 @@
       </c>
       <c r="O102" s="39"/>
       <c r="P102" s="39" t="s">
-        <v>408</v>
+        <v>401</v>
       </c>
       <c r="Q102" s="39">
         <v>1</v>
@@ -15055,7 +15184,7 @@
         <v>125</v>
       </c>
       <c r="AC102" s="39" t="s">
-        <v>399</v>
+        <v>392</v>
       </c>
       <c r="AD102" s="39"/>
       <c r="AE102" s="39"/>
@@ -15065,10 +15194,10 @@
         <v>35003</v>
       </c>
       <c r="B103" s="40" t="s">
-        <v>402</v>
+        <v>395</v>
       </c>
       <c r="C103" s="41" t="s">
-        <v>403</v>
+        <v>396</v>
       </c>
       <c r="D103" s="39" t="str">
         <f t="shared" ref="D103:D107" si="48">"STR_"&amp;UPPER(C103)</f>
@@ -15107,7 +15236,7 @@
       </c>
       <c r="O103" s="39"/>
       <c r="P103" s="39" t="s">
-        <v>408</v>
+        <v>401</v>
       </c>
       <c r="Q103" s="39">
         <v>1</v>
@@ -15136,7 +15265,7 @@
         <v>125</v>
       </c>
       <c r="AC103" s="39" t="s">
-        <v>404</v>
+        <v>397</v>
       </c>
       <c r="AD103" s="39"/>
       <c r="AE103" s="39"/>
@@ -15146,10 +15275,10 @@
         <v>35004</v>
       </c>
       <c r="B104" s="40" t="s">
-        <v>412</v>
+        <v>405</v>
       </c>
       <c r="C104" s="41" t="s">
-        <v>415</v>
+        <v>408</v>
       </c>
       <c r="D104" s="39" t="str">
         <f t="shared" si="48"/>
@@ -15188,7 +15317,7 @@
       </c>
       <c r="O104" s="39"/>
       <c r="P104" s="39" t="s">
-        <v>408</v>
+        <v>401</v>
       </c>
       <c r="Q104" s="39">
         <v>1</v>
@@ -15208,7 +15337,7 @@
         <v>2</v>
       </c>
       <c r="Z104" s="39" t="s">
-        <v>418</v>
+        <v>411</v>
       </c>
       <c r="AA104" s="39">
         <v>1</v>
@@ -15227,10 +15356,10 @@
         <v>35005</v>
       </c>
       <c r="B105" s="40" t="s">
-        <v>413</v>
+        <v>406</v>
       </c>
       <c r="C105" s="41" t="s">
-        <v>416</v>
+        <v>409</v>
       </c>
       <c r="D105" s="39" t="str">
         <f t="shared" ref="D105" si="50">"STR_"&amp;UPPER(C105)</f>
@@ -15269,7 +15398,7 @@
       </c>
       <c r="O105" s="39"/>
       <c r="P105" s="39" t="s">
-        <v>408</v>
+        <v>401</v>
       </c>
       <c r="Q105" s="39">
         <v>1</v>
@@ -15308,10 +15437,10 @@
         <v>35006</v>
       </c>
       <c r="B106" s="40" t="s">
-        <v>414</v>
+        <v>407</v>
       </c>
       <c r="C106" s="41" t="s">
-        <v>417</v>
+        <v>410</v>
       </c>
       <c r="D106" s="39" t="str">
         <f t="shared" si="48"/>
@@ -15350,7 +15479,7 @@
       </c>
       <c r="O106" s="39"/>
       <c r="P106" s="39" t="s">
-        <v>408</v>
+        <v>401</v>
       </c>
       <c r="Q106" s="39">
         <v>1</v>
@@ -15370,7 +15499,7 @@
         <v>2</v>
       </c>
       <c r="Z106" s="39" t="s">
-        <v>411</v>
+        <v>404</v>
       </c>
       <c r="AA106" s="39">
         <v>1</v>
@@ -15389,10 +15518,10 @@
         <v>35007</v>
       </c>
       <c r="B107" s="40" t="s">
-        <v>435</v>
+        <v>428</v>
       </c>
       <c r="C107" s="41" t="s">
-        <v>436</v>
+        <v>429</v>
       </c>
       <c r="D107" s="39" t="str">
         <f t="shared" si="48"/>
@@ -15431,7 +15560,7 @@
       </c>
       <c r="O107" s="39"/>
       <c r="P107" s="39" t="s">
-        <v>408</v>
+        <v>401</v>
       </c>
       <c r="Q107" s="39">
         <v>1</v>
@@ -15460,7 +15589,7 @@
         <v>125</v>
       </c>
       <c r="AC107" s="39" t="s">
-        <v>441</v>
+        <v>434</v>
       </c>
       <c r="AD107" s="39"/>
       <c r="AE107" s="39"/>
@@ -15470,10 +15599,10 @@
         <v>35008</v>
       </c>
       <c r="B108" s="40" t="s">
-        <v>456</v>
+        <v>449</v>
       </c>
       <c r="C108" s="41" t="s">
-        <v>457</v>
+        <v>450</v>
       </c>
       <c r="D108" s="39" t="str">
         <f t="shared" ref="D108" si="52">"STR_"&amp;UPPER(C108)</f>
@@ -15512,7 +15641,7 @@
       </c>
       <c r="O108" s="39"/>
       <c r="P108" s="39" t="s">
-        <v>408</v>
+        <v>401</v>
       </c>
       <c r="Q108" s="39">
         <v>1</v>
@@ -15538,10 +15667,10 @@
         <v>0</v>
       </c>
       <c r="AB108" s="39" t="s">
-        <v>125</v>
+        <v>509</v>
       </c>
       <c r="AC108" s="39" t="s">
-        <v>458</v>
+        <v>451</v>
       </c>
       <c r="AD108" s="39"/>
       <c r="AE108" s="39"/>
@@ -15727,10 +15856,10 @@
         <v>36002</v>
       </c>
       <c r="B111" s="35" t="s">
-        <v>410</v>
+        <v>403</v>
       </c>
       <c r="C111" s="36" t="s">
-        <v>411</v>
+        <v>404</v>
       </c>
       <c r="D111" s="34" t="str">
         <f t="shared" ref="D111" si="54">"STR_"&amp;UPPER(C111)</f>
@@ -15906,10 +16035,10 @@
         <v>38001</v>
       </c>
       <c r="B113" s="40" t="s">
-        <v>459</v>
+        <v>452</v>
       </c>
       <c r="C113" s="41" t="s">
-        <v>460</v>
+        <v>453</v>
       </c>
       <c r="D113" s="39" t="str">
         <f t="shared" ref="D113" si="56">"STR_"&amp;UPPER(C113)</f>
@@ -15980,7 +16109,7 @@
         <v>0</v>
       </c>
       <c r="AB113" s="39" t="s">
-        <v>463</v>
+        <v>456</v>
       </c>
       <c r="AC113" s="39" t="s">
         <v>41</v>
@@ -15997,10 +16126,10 @@
         <v>38002</v>
       </c>
       <c r="B114" s="40" t="s">
-        <v>461</v>
+        <v>454</v>
       </c>
       <c r="C114" s="41" t="s">
-        <v>462</v>
+        <v>455</v>
       </c>
       <c r="D114" s="39" t="str">
         <f t="shared" ref="D114" si="58">"STR_"&amp;UPPER(C114)</f>
@@ -16071,7 +16200,7 @@
         <v>0</v>
       </c>
       <c r="AB114" s="39" t="s">
-        <v>464</v>
+        <v>457</v>
       </c>
       <c r="AC114" s="39" t="s">
         <v>41</v>
@@ -16084,116 +16213,119 @@
       </c>
     </row>
     <row r="115" spans="1:31" x14ac:dyDescent="0.3">
-      <c r="A115" s="34">
-        <v>38500</v>
-      </c>
-      <c r="B115" s="35" t="s">
-        <v>171</v>
-      </c>
-      <c r="C115" s="36" t="s">
-        <v>113</v>
-      </c>
-      <c r="D115" s="34" t="str">
-        <f t="shared" si="44"/>
-        <v>STR_ITEM_METERIAL_01</v>
-      </c>
-      <c r="E115" s="34" t="str">
-        <f t="shared" si="45"/>
-        <v>STR_ITEM_METERIAL_01_DESC</v>
-      </c>
-      <c r="F115" s="34">
-        <v>0</v>
-      </c>
-      <c r="G115" s="34" t="s">
-        <v>56</v>
-      </c>
-      <c r="H115" s="34">
-        <v>0</v>
-      </c>
-      <c r="I115" s="34">
-        <v>0</v>
-      </c>
-      <c r="J115" s="34">
-        <v>0</v>
-      </c>
-      <c r="K115" s="34">
-        <v>0</v>
-      </c>
-      <c r="L115" s="34">
-        <v>0</v>
-      </c>
-      <c r="M115" s="34">
-        <v>0</v>
-      </c>
-      <c r="N115" s="34">
-        <v>0</v>
-      </c>
-      <c r="P115" s="34" t="s">
+      <c r="A115" s="39">
+        <v>38003</v>
+      </c>
+      <c r="B115" s="40" t="s">
+        <v>510</v>
+      </c>
+      <c r="C115" s="41" t="s">
+        <v>511</v>
+      </c>
+      <c r="D115" s="39" t="str">
+        <f t="shared" ref="D115" si="60">"STR_"&amp;UPPER(C115)</f>
+        <v>STR_ITEM_QUEST_04</v>
+      </c>
+      <c r="E115" s="39" t="str">
+        <f t="shared" ref="E115" si="61">D115&amp;"_DESC"</f>
+        <v>STR_ITEM_QUEST_04_DESC</v>
+      </c>
+      <c r="F115" s="39">
+        <v>1</v>
+      </c>
+      <c r="G115" s="39" t="s">
+        <v>54</v>
+      </c>
+      <c r="H115" s="39">
+        <v>0</v>
+      </c>
+      <c r="I115" s="39">
+        <v>0</v>
+      </c>
+      <c r="J115" s="39">
+        <v>0</v>
+      </c>
+      <c r="K115" s="39">
+        <v>0</v>
+      </c>
+      <c r="L115" s="39">
+        <v>0</v>
+      </c>
+      <c r="M115" s="39">
+        <v>0</v>
+      </c>
+      <c r="N115" s="39">
+        <v>0</v>
+      </c>
+      <c r="O115" s="39"/>
+      <c r="P115" s="39" t="s">
         <v>44</v>
       </c>
-      <c r="Q115" s="34">
-        <v>0</v>
-      </c>
-      <c r="R115" s="37" t="s">
-        <v>41</v>
-      </c>
-      <c r="U115" s="37" t="s">
-        <v>41</v>
-      </c>
-      <c r="V115" s="37" t="s">
-        <v>41</v>
-      </c>
-      <c r="W115" s="34" t="b">
-        <v>1</v>
-      </c>
-      <c r="X115" s="34">
+      <c r="Q115" s="39">
+        <v>0</v>
+      </c>
+      <c r="R115" s="39" t="s">
+        <v>41</v>
+      </c>
+      <c r="S115" s="39"/>
+      <c r="T115" s="39"/>
+      <c r="U115" s="39" t="s">
+        <v>41</v>
+      </c>
+      <c r="V115" s="39" t="s">
+        <v>41</v>
+      </c>
+      <c r="W115" s="39" t="b">
+        <v>0</v>
+      </c>
+      <c r="X115" s="39">
         <v>10</v>
       </c>
-      <c r="Y115" s="34">
-        <v>0</v>
-      </c>
-      <c r="Z115" s="34" t="s">
-        <v>41</v>
-      </c>
-      <c r="AA115" s="37">
-        <v>0</v>
-      </c>
-      <c r="AB115" s="37" t="s">
-        <v>125</v>
-      </c>
-      <c r="AC115" s="37" t="s">
-        <v>41</v>
-      </c>
-      <c r="AD115" s="37" t="s">
-        <v>41</v>
-      </c>
-      <c r="AE115" s="37" t="s">
+      <c r="Y115" s="39">
+        <v>0</v>
+      </c>
+      <c r="Z115" s="39" t="s">
+        <v>41</v>
+      </c>
+      <c r="AA115" s="39">
+        <v>0</v>
+      </c>
+      <c r="AB115" s="39" t="s">
+        <v>512</v>
+      </c>
+      <c r="AC115" s="39" t="s">
+        <v>41</v>
+      </c>
+      <c r="AD115" s="39" t="s">
+        <v>41</v>
+      </c>
+      <c r="AE115" s="39" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="116" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A116" s="39">
-        <v>39000</v>
+        <v>38004</v>
       </c>
       <c r="B116" s="40" t="s">
-        <v>172</v>
+        <v>513</v>
       </c>
       <c r="C116" s="41" t="s">
-        <v>162</v>
+        <v>514</v>
       </c>
       <c r="D116" s="39" t="str">
-        <f t="shared" si="44"/>
-        <v>STR_ITEM_POTION_ITEMSLOT_01</v>
+        <f t="shared" ref="D116" si="62">"STR_"&amp;UPPER(C116)</f>
+        <v>STR_ITEM_QUEST_05</v>
       </c>
       <c r="E116" s="39" t="str">
-        <f t="shared" si="45"/>
-        <v>STR_ITEM_POTION_ITEMSLOT_01_DESC</v>
+        <f t="shared" ref="E116" si="63">D116&amp;"_DESC"</f>
+        <v>STR_ITEM_QUEST_05_DESC</v>
       </c>
       <c r="F116" s="39">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G116" s="39" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="H116" s="39">
         <v>0</v>
@@ -16218,10 +16350,10 @@
       </c>
       <c r="O116" s="39"/>
       <c r="P116" s="39" t="s">
-        <v>163</v>
+        <v>44</v>
       </c>
       <c r="Q116" s="39">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="R116" s="39" t="s">
         <v>41</v>
@@ -16241,7 +16373,7 @@
         <v>10</v>
       </c>
       <c r="Y116" s="39">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="Z116" s="39" t="s">
         <v>41</v>
@@ -16250,7 +16382,7 @@
         <v>0</v>
       </c>
       <c r="AB116" s="39" t="s">
-        <v>302</v>
+        <v>512</v>
       </c>
       <c r="AC116" s="39" t="s">
         <v>41</v>
@@ -16264,27 +16396,27 @@
     </row>
     <row r="117" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A117" s="39">
-        <v>39001</v>
+        <v>38005</v>
       </c>
       <c r="B117" s="40" t="s">
-        <v>173</v>
+        <v>516</v>
       </c>
       <c r="C117" s="41" t="s">
-        <v>166</v>
+        <v>515</v>
       </c>
       <c r="D117" s="39" t="str">
-        <f t="shared" ref="D117" si="60">"STR_"&amp;UPPER(C117)</f>
-        <v>STR_ITEM_POTION_SLOT_01</v>
+        <f t="shared" ref="D117" si="64">"STR_"&amp;UPPER(C117)</f>
+        <v>STR_ITEM_QUEST_06</v>
       </c>
       <c r="E117" s="39" t="str">
-        <f t="shared" ref="E117" si="61">D117&amp;"_DESC"</f>
-        <v>STR_ITEM_POTION_SLOT_01_DESC</v>
+        <f t="shared" ref="E117" si="65">D117&amp;"_DESC"</f>
+        <v>STR_ITEM_QUEST_06_DESC</v>
       </c>
       <c r="F117" s="39">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G117" s="39" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="H117" s="39">
         <v>0</v>
@@ -16309,10 +16441,10 @@
       </c>
       <c r="O117" s="39"/>
       <c r="P117" s="39" t="s">
-        <v>263</v>
+        <v>44</v>
       </c>
       <c r="Q117" s="39">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R117" s="39" t="s">
         <v>41</v>
@@ -16326,13 +16458,13 @@
         <v>41</v>
       </c>
       <c r="W117" s="39" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X117" s="39">
         <v>10</v>
       </c>
       <c r="Y117" s="39">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="Z117" s="39" t="s">
         <v>41</v>
@@ -16341,7 +16473,7 @@
         <v>0</v>
       </c>
       <c r="AB117" s="39" t="s">
-        <v>303</v>
+        <v>512</v>
       </c>
       <c r="AC117" s="39" t="s">
         <v>41</v>
@@ -16354,116 +16486,113 @@
       </c>
     </row>
     <row r="118" spans="1:31" x14ac:dyDescent="0.3">
-      <c r="A118" s="39">
-        <v>39002</v>
-      </c>
-      <c r="B118" s="40" t="s">
-        <v>440</v>
-      </c>
-      <c r="C118" s="41" t="s">
-        <v>437</v>
-      </c>
-      <c r="D118" s="39" t="str">
-        <f t="shared" ref="D118" si="62">"STR_"&amp;UPPER(C118)</f>
-        <v>STR_ITEM_SUMMON_01</v>
-      </c>
-      <c r="E118" s="39" t="str">
-        <f t="shared" ref="E118" si="63">D118&amp;"_DESC"</f>
-        <v>STR_ITEM_SUMMON_01_DESC</v>
-      </c>
-      <c r="F118" s="39">
-        <v>4</v>
-      </c>
-      <c r="G118" s="39" t="s">
-        <v>48</v>
-      </c>
-      <c r="H118" s="39">
-        <v>0</v>
-      </c>
-      <c r="I118" s="39">
-        <v>0</v>
-      </c>
-      <c r="J118" s="39">
-        <v>0</v>
-      </c>
-      <c r="K118" s="39">
-        <v>0</v>
-      </c>
-      <c r="L118" s="39">
-        <v>0</v>
-      </c>
-      <c r="M118" s="39">
-        <v>0</v>
-      </c>
-      <c r="N118" s="39">
-        <v>0</v>
-      </c>
-      <c r="O118" s="39"/>
-      <c r="P118" s="39" t="s">
-        <v>438</v>
-      </c>
-      <c r="Q118" s="39">
-        <v>10017</v>
-      </c>
-      <c r="R118" s="39" t="s">
-        <v>41</v>
-      </c>
-      <c r="S118" s="39"/>
-      <c r="T118" s="39"/>
-      <c r="U118" s="39" t="s">
-        <v>41</v>
-      </c>
-      <c r="V118" s="39" t="s">
-        <v>41</v>
-      </c>
-      <c r="W118" s="39" t="b">
+      <c r="A118" s="34">
+        <v>38500</v>
+      </c>
+      <c r="B118" s="35" t="s">
+        <v>171</v>
+      </c>
+      <c r="C118" s="36" t="s">
+        <v>113</v>
+      </c>
+      <c r="D118" s="34" t="str">
+        <f t="shared" si="44"/>
+        <v>STR_ITEM_METERIAL_01</v>
+      </c>
+      <c r="E118" s="34" t="str">
+        <f t="shared" si="45"/>
+        <v>STR_ITEM_METERIAL_01_DESC</v>
+      </c>
+      <c r="F118" s="34">
+        <v>0</v>
+      </c>
+      <c r="G118" s="34" t="s">
+        <v>56</v>
+      </c>
+      <c r="H118" s="34">
+        <v>0</v>
+      </c>
+      <c r="I118" s="34">
+        <v>0</v>
+      </c>
+      <c r="J118" s="34">
+        <v>0</v>
+      </c>
+      <c r="K118" s="34">
+        <v>0</v>
+      </c>
+      <c r="L118" s="34">
+        <v>0</v>
+      </c>
+      <c r="M118" s="34">
+        <v>0</v>
+      </c>
+      <c r="N118" s="34">
+        <v>0</v>
+      </c>
+      <c r="P118" s="34" t="s">
+        <v>44</v>
+      </c>
+      <c r="Q118" s="34">
+        <v>0</v>
+      </c>
+      <c r="R118" s="37" t="s">
+        <v>41</v>
+      </c>
+      <c r="U118" s="37" t="s">
+        <v>41</v>
+      </c>
+      <c r="V118" s="37" t="s">
+        <v>41</v>
+      </c>
+      <c r="W118" s="34" t="b">
         <v>1</v>
       </c>
-      <c r="X118" s="39">
+      <c r="X118" s="34">
         <v>10</v>
       </c>
-      <c r="Y118" s="39">
+      <c r="Y118" s="34">
+        <v>0</v>
+      </c>
+      <c r="Z118" s="34" t="s">
+        <v>41</v>
+      </c>
+      <c r="AA118" s="37">
+        <v>0</v>
+      </c>
+      <c r="AB118" s="37" t="s">
         <v>125</v>
       </c>
-      <c r="Z118" s="39" t="s">
-        <v>41</v>
-      </c>
-      <c r="AA118" s="39">
-        <v>0</v>
-      </c>
-      <c r="AB118" s="39" t="s">
-        <v>439</v>
-      </c>
-      <c r="AC118" s="39" t="s">
-        <v>41</v>
-      </c>
-      <c r="AD118" s="39" t="s">
-        <v>41</v>
-      </c>
-      <c r="AE118" s="39" t="s">
+      <c r="AC118" s="37" t="s">
+        <v>41</v>
+      </c>
+      <c r="AD118" s="37" t="s">
+        <v>41</v>
+      </c>
+      <c r="AE118" s="37" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="119" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A119" s="39">
-        <v>39003</v>
+        <v>39000</v>
       </c>
       <c r="B119" s="40" t="s">
-        <v>446</v>
+        <v>172</v>
       </c>
       <c r="C119" s="41" t="s">
-        <v>442</v>
+        <v>162</v>
       </c>
       <c r="D119" s="39" t="str">
-        <f t="shared" ref="D119:D121" si="64">"STR_"&amp;UPPER(C119)</f>
-        <v>STR_ITEM_SUMMON_02</v>
+        <f t="shared" si="44"/>
+        <v>STR_ITEM_POTION_ITEMSLOT_01</v>
       </c>
       <c r="E119" s="39" t="str">
-        <f t="shared" ref="E119:E121" si="65">D119&amp;"_DESC"</f>
-        <v>STR_ITEM_SUMMON_02_DESC</v>
+        <f t="shared" si="45"/>
+        <v>STR_ITEM_POTION_ITEMSLOT_01_DESC</v>
       </c>
       <c r="F119" s="39">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G119" s="39" t="s">
         <v>48</v>
@@ -16491,10 +16620,10 @@
       </c>
       <c r="O119" s="39"/>
       <c r="P119" s="39" t="s">
-        <v>438</v>
+        <v>163</v>
       </c>
       <c r="Q119" s="39">
-        <v>10018</v>
+        <v>5</v>
       </c>
       <c r="R119" s="39" t="s">
         <v>41</v>
@@ -16514,7 +16643,7 @@
         <v>10</v>
       </c>
       <c r="Y119" s="39">
-        <v>125</v>
+        <v>25</v>
       </c>
       <c r="Z119" s="39" t="s">
         <v>41</v>
@@ -16523,7 +16652,7 @@
         <v>0</v>
       </c>
       <c r="AB119" s="39" t="s">
-        <v>439</v>
+        <v>302</v>
       </c>
       <c r="AC119" s="39" t="s">
         <v>41</v>
@@ -16537,24 +16666,24 @@
     </row>
     <row r="120" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A120" s="39">
-        <v>39004</v>
+        <v>39001</v>
       </c>
       <c r="B120" s="40" t="s">
-        <v>447</v>
+        <v>173</v>
       </c>
       <c r="C120" s="41" t="s">
-        <v>443</v>
+        <v>166</v>
       </c>
       <c r="D120" s="39" t="str">
-        <f t="shared" si="64"/>
-        <v>STR_ITEM_SUMMON_03</v>
+        <f t="shared" ref="D120" si="66">"STR_"&amp;UPPER(C120)</f>
+        <v>STR_ITEM_POTION_SLOT_01</v>
       </c>
       <c r="E120" s="39" t="str">
-        <f t="shared" si="65"/>
-        <v>STR_ITEM_SUMMON_03_DESC</v>
+        <f t="shared" ref="E120" si="67">D120&amp;"_DESC"</f>
+        <v>STR_ITEM_POTION_SLOT_01_DESC</v>
       </c>
       <c r="F120" s="39">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G120" s="39" t="s">
         <v>48</v>
@@ -16582,10 +16711,10 @@
       </c>
       <c r="O120" s="39"/>
       <c r="P120" s="39" t="s">
-        <v>438</v>
+        <v>263</v>
       </c>
       <c r="Q120" s="39">
-        <v>10019</v>
+        <v>1</v>
       </c>
       <c r="R120" s="39" t="s">
         <v>41</v>
@@ -16605,7 +16734,7 @@
         <v>10</v>
       </c>
       <c r="Y120" s="39">
-        <v>125</v>
+        <v>50</v>
       </c>
       <c r="Z120" s="39" t="s">
         <v>41</v>
@@ -16614,7 +16743,7 @@
         <v>0</v>
       </c>
       <c r="AB120" s="39" t="s">
-        <v>439</v>
+        <v>303</v>
       </c>
       <c r="AC120" s="39" t="s">
         <v>41</v>
@@ -16628,21 +16757,21 @@
     </row>
     <row r="121" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A121" s="39">
-        <v>39005</v>
+        <v>39002</v>
       </c>
       <c r="B121" s="40" t="s">
-        <v>448</v>
+        <v>433</v>
       </c>
       <c r="C121" s="41" t="s">
-        <v>444</v>
+        <v>430</v>
       </c>
       <c r="D121" s="39" t="str">
-        <f t="shared" si="64"/>
-        <v>STR_ITEM_SUMMON_04</v>
+        <f t="shared" ref="D121" si="68">"STR_"&amp;UPPER(C121)</f>
+        <v>STR_ITEM_SUMMON_01</v>
       </c>
       <c r="E121" s="39" t="str">
-        <f t="shared" si="65"/>
-        <v>STR_ITEM_SUMMON_04_DESC</v>
+        <f t="shared" ref="E121" si="69">D121&amp;"_DESC"</f>
+        <v>STR_ITEM_SUMMON_01_DESC</v>
       </c>
       <c r="F121" s="39">
         <v>4</v>
@@ -16673,10 +16802,10 @@
       </c>
       <c r="O121" s="39"/>
       <c r="P121" s="39" t="s">
-        <v>438</v>
+        <v>431</v>
       </c>
       <c r="Q121" s="39">
-        <v>10020</v>
+        <v>10017</v>
       </c>
       <c r="R121" s="39" t="s">
         <v>41</v>
@@ -16705,7 +16834,7 @@
         <v>0</v>
       </c>
       <c r="AB121" s="39" t="s">
-        <v>439</v>
+        <v>432</v>
       </c>
       <c r="AC121" s="39" t="s">
         <v>41</v>
@@ -16719,21 +16848,21 @@
     </row>
     <row r="122" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A122" s="39">
-        <v>39006</v>
+        <v>39003</v>
       </c>
       <c r="B122" s="40" t="s">
-        <v>449</v>
+        <v>439</v>
       </c>
       <c r="C122" s="41" t="s">
-        <v>445</v>
+        <v>435</v>
       </c>
       <c r="D122" s="39" t="str">
-        <f t="shared" ref="D122" si="66">"STR_"&amp;UPPER(C122)</f>
-        <v>STR_ITEM_SUMMON_05</v>
+        <f t="shared" ref="D122:D124" si="70">"STR_"&amp;UPPER(C122)</f>
+        <v>STR_ITEM_SUMMON_02</v>
       </c>
       <c r="E122" s="39" t="str">
-        <f t="shared" ref="E122" si="67">D122&amp;"_DESC"</f>
-        <v>STR_ITEM_SUMMON_05_DESC</v>
+        <f t="shared" ref="E122:E124" si="71">D122&amp;"_DESC"</f>
+        <v>STR_ITEM_SUMMON_02_DESC</v>
       </c>
       <c r="F122" s="39">
         <v>4</v>
@@ -16764,10 +16893,10 @@
       </c>
       <c r="O122" s="39"/>
       <c r="P122" s="39" t="s">
-        <v>438</v>
+        <v>431</v>
       </c>
       <c r="Q122" s="39">
-        <v>10021</v>
+        <v>10018</v>
       </c>
       <c r="R122" s="39" t="s">
         <v>41</v>
@@ -16796,7 +16925,7 @@
         <v>0</v>
       </c>
       <c r="AB122" s="39" t="s">
-        <v>439</v>
+        <v>432</v>
       </c>
       <c r="AC122" s="39" t="s">
         <v>41</v>
@@ -16805,6 +16934,279 @@
         <v>41</v>
       </c>
       <c r="AE122" s="39" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="123" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="A123" s="39">
+        <v>39004</v>
+      </c>
+      <c r="B123" s="40" t="s">
+        <v>440</v>
+      </c>
+      <c r="C123" s="41" t="s">
+        <v>436</v>
+      </c>
+      <c r="D123" s="39" t="str">
+        <f t="shared" si="70"/>
+        <v>STR_ITEM_SUMMON_03</v>
+      </c>
+      <c r="E123" s="39" t="str">
+        <f t="shared" si="71"/>
+        <v>STR_ITEM_SUMMON_03_DESC</v>
+      </c>
+      <c r="F123" s="39">
+        <v>4</v>
+      </c>
+      <c r="G123" s="39" t="s">
+        <v>48</v>
+      </c>
+      <c r="H123" s="39">
+        <v>0</v>
+      </c>
+      <c r="I123" s="39">
+        <v>0</v>
+      </c>
+      <c r="J123" s="39">
+        <v>0</v>
+      </c>
+      <c r="K123" s="39">
+        <v>0</v>
+      </c>
+      <c r="L123" s="39">
+        <v>0</v>
+      </c>
+      <c r="M123" s="39">
+        <v>0</v>
+      </c>
+      <c r="N123" s="39">
+        <v>0</v>
+      </c>
+      <c r="O123" s="39"/>
+      <c r="P123" s="39" t="s">
+        <v>431</v>
+      </c>
+      <c r="Q123" s="39">
+        <v>10019</v>
+      </c>
+      <c r="R123" s="39" t="s">
+        <v>41</v>
+      </c>
+      <c r="S123" s="39"/>
+      <c r="T123" s="39"/>
+      <c r="U123" s="39" t="s">
+        <v>41</v>
+      </c>
+      <c r="V123" s="39" t="s">
+        <v>41</v>
+      </c>
+      <c r="W123" s="39" t="b">
+        <v>1</v>
+      </c>
+      <c r="X123" s="39">
+        <v>10</v>
+      </c>
+      <c r="Y123" s="39">
+        <v>125</v>
+      </c>
+      <c r="Z123" s="39" t="s">
+        <v>41</v>
+      </c>
+      <c r="AA123" s="39">
+        <v>0</v>
+      </c>
+      <c r="AB123" s="39" t="s">
+        <v>432</v>
+      </c>
+      <c r="AC123" s="39" t="s">
+        <v>41</v>
+      </c>
+      <c r="AD123" s="39" t="s">
+        <v>41</v>
+      </c>
+      <c r="AE123" s="39" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="124" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="A124" s="39">
+        <v>39005</v>
+      </c>
+      <c r="B124" s="40" t="s">
+        <v>441</v>
+      </c>
+      <c r="C124" s="41" t="s">
+        <v>437</v>
+      </c>
+      <c r="D124" s="39" t="str">
+        <f t="shared" si="70"/>
+        <v>STR_ITEM_SUMMON_04</v>
+      </c>
+      <c r="E124" s="39" t="str">
+        <f t="shared" si="71"/>
+        <v>STR_ITEM_SUMMON_04_DESC</v>
+      </c>
+      <c r="F124" s="39">
+        <v>4</v>
+      </c>
+      <c r="G124" s="39" t="s">
+        <v>48</v>
+      </c>
+      <c r="H124" s="39">
+        <v>0</v>
+      </c>
+      <c r="I124" s="39">
+        <v>0</v>
+      </c>
+      <c r="J124" s="39">
+        <v>0</v>
+      </c>
+      <c r="K124" s="39">
+        <v>0</v>
+      </c>
+      <c r="L124" s="39">
+        <v>0</v>
+      </c>
+      <c r="M124" s="39">
+        <v>0</v>
+      </c>
+      <c r="N124" s="39">
+        <v>0</v>
+      </c>
+      <c r="O124" s="39"/>
+      <c r="P124" s="39" t="s">
+        <v>431</v>
+      </c>
+      <c r="Q124" s="39">
+        <v>10020</v>
+      </c>
+      <c r="R124" s="39" t="s">
+        <v>41</v>
+      </c>
+      <c r="S124" s="39"/>
+      <c r="T124" s="39"/>
+      <c r="U124" s="39" t="s">
+        <v>41</v>
+      </c>
+      <c r="V124" s="39" t="s">
+        <v>41</v>
+      </c>
+      <c r="W124" s="39" t="b">
+        <v>1</v>
+      </c>
+      <c r="X124" s="39">
+        <v>10</v>
+      </c>
+      <c r="Y124" s="39">
+        <v>125</v>
+      </c>
+      <c r="Z124" s="39" t="s">
+        <v>41</v>
+      </c>
+      <c r="AA124" s="39">
+        <v>0</v>
+      </c>
+      <c r="AB124" s="39" t="s">
+        <v>432</v>
+      </c>
+      <c r="AC124" s="39" t="s">
+        <v>41</v>
+      </c>
+      <c r="AD124" s="39" t="s">
+        <v>41</v>
+      </c>
+      <c r="AE124" s="39" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="125" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="A125" s="39">
+        <v>39006</v>
+      </c>
+      <c r="B125" s="40" t="s">
+        <v>442</v>
+      </c>
+      <c r="C125" s="41" t="s">
+        <v>438</v>
+      </c>
+      <c r="D125" s="39" t="str">
+        <f t="shared" ref="D125" si="72">"STR_"&amp;UPPER(C125)</f>
+        <v>STR_ITEM_SUMMON_05</v>
+      </c>
+      <c r="E125" s="39" t="str">
+        <f t="shared" ref="E125" si="73">D125&amp;"_DESC"</f>
+        <v>STR_ITEM_SUMMON_05_DESC</v>
+      </c>
+      <c r="F125" s="39">
+        <v>4</v>
+      </c>
+      <c r="G125" s="39" t="s">
+        <v>48</v>
+      </c>
+      <c r="H125" s="39">
+        <v>0</v>
+      </c>
+      <c r="I125" s="39">
+        <v>0</v>
+      </c>
+      <c r="J125" s="39">
+        <v>0</v>
+      </c>
+      <c r="K125" s="39">
+        <v>0</v>
+      </c>
+      <c r="L125" s="39">
+        <v>0</v>
+      </c>
+      <c r="M125" s="39">
+        <v>0</v>
+      </c>
+      <c r="N125" s="39">
+        <v>0</v>
+      </c>
+      <c r="O125" s="39"/>
+      <c r="P125" s="39" t="s">
+        <v>431</v>
+      </c>
+      <c r="Q125" s="39">
+        <v>10021</v>
+      </c>
+      <c r="R125" s="39" t="s">
+        <v>41</v>
+      </c>
+      <c r="S125" s="39"/>
+      <c r="T125" s="39"/>
+      <c r="U125" s="39" t="s">
+        <v>41</v>
+      </c>
+      <c r="V125" s="39" t="s">
+        <v>41</v>
+      </c>
+      <c r="W125" s="39" t="b">
+        <v>1</v>
+      </c>
+      <c r="X125" s="39">
+        <v>10</v>
+      </c>
+      <c r="Y125" s="39">
+        <v>125</v>
+      </c>
+      <c r="Z125" s="39" t="s">
+        <v>41</v>
+      </c>
+      <c r="AA125" s="39">
+        <v>0</v>
+      </c>
+      <c r="AB125" s="39" t="s">
+        <v>432</v>
+      </c>
+      <c r="AC125" s="39" t="s">
+        <v>41</v>
+      </c>
+      <c r="AD125" s="39" t="s">
+        <v>41</v>
+      </c>
+      <c r="AE125" s="39" t="s">
         <v>41</v>
       </c>
     </row>
@@ -16823,7 +17225,7 @@
           <x14:formula2>
             <xm:f>Definition!#REF!</xm:f>
           </x14:formula2>
-          <xm:sqref>F115</xm:sqref>
+          <xm:sqref>F118</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
@@ -16832,7 +17234,7 @@
           <x14:formula2>
             <xm:f>Definition!G32</xm:f>
           </x14:formula2>
-          <xm:sqref>F116:F122</xm:sqref>
+          <xm:sqref>F119:F125</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
@@ -16841,13 +17243,13 @@
           <x14:formula2>
             <xm:f>Definition!G32</xm:f>
           </x14:formula2>
-          <xm:sqref>H115:H122</xm:sqref>
+          <xm:sqref>H118:H125</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>Type!$B$2:$B$20</xm:f>
           </x14:formula1>
-          <xm:sqref>P2:P122</xm:sqref>
+          <xm:sqref>P2:P125</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
@@ -16862,7 +17264,7 @@
           <x14:formula2>
             <xm:f>Definition!G35</xm:f>
           </x14:formula2>
-          <xm:sqref>F112:F114</xm:sqref>
+          <xm:sqref>F112:F117</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
@@ -16889,7 +17291,7 @@
           <x14:formula2>
             <xm:f>Definition!G31</xm:f>
           </x14:formula2>
-          <xm:sqref>H112:H114</xm:sqref>
+          <xm:sqref>H112:H117</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
@@ -16970,7 +17372,7 @@
           <x14:formula2>
             <xm:f>Definition!G24</xm:f>
           </x14:formula2>
-          <xm:sqref>F85:F87 F50 F58 F54 F62</xm:sqref>
+          <xm:sqref>F85:F87 F62 F54 F58 F50</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
@@ -17078,7 +17480,7 @@
           <x14:formula2>
             <xm:f>Definition!G34</xm:f>
           </x14:formula2>
-          <xm:sqref>F73:F75 F55:F57 F59:F61 F51:F53</xm:sqref>
+          <xm:sqref>F73:F75 F51:F53 F59:F61 F55:F57</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
@@ -17087,7 +17489,7 @@
           <x14:formula2>
             <xm:f>Definition!G38</xm:f>
           </x14:formula2>
-          <xm:sqref>H73:H75 H57 H61 H53</xm:sqref>
+          <xm:sqref>H73:H75 H53 H61 H57</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
@@ -17150,7 +17552,7 @@
           <x14:formula2>
             <xm:f>Definition!G29</xm:f>
           </x14:formula2>
-          <xm:sqref>H50:H52 H58:H60 H54:H56 H62</xm:sqref>
+          <xm:sqref>H50:H52 H62 H54:H56 H58:H60</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
@@ -17544,7 +17946,7 @@
         <v>55</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>409</v>
+        <v>402</v>
       </c>
       <c r="C7" s="1"/>
       <c r="D7" s="1"/>
